--- a/doc/state_mapping.xlsx
+++ b/doc/state_mapping.xlsx
@@ -16227,14 +16227,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -16244,8 +16245,13 @@
       <c r="C1" s="2" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>346</v>
       </c>
@@ -16255,8 +16261,11 @@
       <c r="C2" s="4" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>346</v>
       </c>
@@ -16266,8 +16275,11 @@
       <c r="C3" s="4" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>346</v>
       </c>
@@ -16277,8 +16289,11 @@
       <c r="C4" s="4" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>346</v>
       </c>
@@ -16288,8 +16303,11 @@
       <c r="C5" s="4" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>346</v>
       </c>
@@ -16299,8 +16317,11 @@
       <c r="C6" s="4" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>346</v>
       </c>
@@ -16310,8 +16331,11 @@
       <c r="C7" s="4" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>346</v>
       </c>
@@ -16321,8 +16345,11 @@
       <c r="C8" s="4" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>346</v>
       </c>
@@ -16332,8 +16359,11 @@
       <c r="C9" s="4" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>346</v>
       </c>
@@ -16343,8 +16373,11 @@
       <c r="C10" s="4" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>346</v>
       </c>
@@ -16354,8 +16387,11 @@
       <c r="C11" s="4" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>346</v>
       </c>
@@ -16365,8 +16401,11 @@
       <c r="C12" s="4" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>346</v>
       </c>
@@ -16376,8 +16415,11 @@
       <c r="C13" s="4" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>346</v>
       </c>
@@ -16387,8 +16429,11 @@
       <c r="C14" s="4" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>346</v>
       </c>
@@ -16398,8 +16443,11 @@
       <c r="C15" s="4" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>346</v>
       </c>
@@ -16409,8 +16457,11 @@
       <c r="C16" s="4" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>346</v>
       </c>
@@ -16420,8 +16471,11 @@
       <c r="C17" s="4" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>346</v>
       </c>
@@ -16431,8 +16485,11 @@
       <c r="C18" s="4" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>346</v>
       </c>
@@ -16442,8 +16499,11 @@
       <c r="C19" s="4" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>346</v>
       </c>
@@ -16453,8 +16513,11 @@
       <c r="C20" s="4" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>346</v>
       </c>
@@ -16464,8 +16527,11 @@
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>346</v>
       </c>
@@ -16475,8 +16541,11 @@
       <c r="C22" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>346</v>
       </c>
@@ -16486,8 +16555,11 @@
       <c r="C23" s="4" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>346</v>
       </c>
@@ -16497,8 +16569,11 @@
       <c r="C24" s="4" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>346</v>
       </c>
@@ -16508,8 +16583,11 @@
       <c r="C25" s="4" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>346</v>
       </c>
@@ -16519,8 +16597,11 @@
       <c r="C26" s="4" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>346</v>
       </c>
@@ -16530,8 +16611,11 @@
       <c r="C27" s="4" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>346</v>
       </c>
@@ -16541,8 +16625,11 @@
       <c r="C28" s="4" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>346</v>
       </c>
@@ -16552,8 +16639,11 @@
       <c r="C29" s="4" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>346</v>
       </c>
@@ -16563,8 +16653,11 @@
       <c r="C30" s="4" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>346</v>
       </c>
@@ -16574,8 +16667,11 @@
       <c r="C31" s="4" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>346</v>
       </c>
@@ -16585,8 +16681,11 @@
       <c r="C32" s="4" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D32" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>346</v>
       </c>
@@ -16596,8 +16695,11 @@
       <c r="C33" s="4" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D33" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>346</v>
       </c>
@@ -16607,8 +16709,11 @@
       <c r="C34" s="4" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D34" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>346</v>
       </c>
@@ -16618,8 +16723,11 @@
       <c r="C35" s="4" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>346</v>
       </c>
@@ -16629,8 +16737,11 @@
       <c r="C36" s="4" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D36" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>346</v>
       </c>
@@ -16640,8 +16751,11 @@
       <c r="C37" s="4" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>346</v>
       </c>
@@ -16651,8 +16765,11 @@
       <c r="C38" s="4" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>346</v>
       </c>
@@ -16662,8 +16779,11 @@
       <c r="C39" s="4" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>346</v>
       </c>
@@ -16673,8 +16793,11 @@
       <c r="C40" s="4" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>346</v>
       </c>
@@ -16684,8 +16807,11 @@
       <c r="C41" s="4" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>346</v>
       </c>
@@ -16695,8 +16821,11 @@
       <c r="C42" s="4" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D42" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>346</v>
       </c>
@@ -16706,8 +16835,11 @@
       <c r="C43" s="4" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D43" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>346</v>
       </c>
@@ -16717,8 +16849,11 @@
       <c r="C44" s="4" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D44" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>346</v>
       </c>
@@ -16728,8 +16863,11 @@
       <c r="C45" s="4" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>346</v>
       </c>
@@ -16739,8 +16877,11 @@
       <c r="C46" s="4" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D46" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>346</v>
       </c>
@@ -16750,8 +16891,11 @@
       <c r="C47" s="4" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D47" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>346</v>
       </c>
@@ -16761,8 +16905,11 @@
       <c r="C48" s="4" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D48" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>346</v>
       </c>
@@ -16772,8 +16919,11 @@
       <c r="C49" s="4" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>346</v>
       </c>
@@ -16783,8 +16933,11 @@
       <c r="C50" s="4" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D50" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>346</v>
       </c>
@@ -16794,8 +16947,11 @@
       <c r="C51" s="4" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D51" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>346</v>
       </c>
@@ -16805,8 +16961,11 @@
       <c r="C52" s="4" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D52" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>346</v>
       </c>
@@ -16816,8 +16975,11 @@
       <c r="C53" s="4" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D53" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -16827,8 +16989,11 @@
       <c r="C54" s="4" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D54" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>346</v>
       </c>
@@ -16838,8 +17003,11 @@
       <c r="C55" s="4" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D55" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>346</v>
       </c>
@@ -16849,8 +17017,11 @@
       <c r="C56" s="4" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D56" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>346</v>
       </c>
@@ -16860,8 +17031,11 @@
       <c r="C57" s="4" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>346</v>
       </c>
@@ -16871,8 +17045,11 @@
       <c r="C58" s="4" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D58" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>346</v>
       </c>
@@ -16882,8 +17059,11 @@
       <c r="C59" s="4" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D59" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>346</v>
       </c>
@@ -16893,8 +17073,11 @@
       <c r="C60" s="4" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D60" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>346</v>
       </c>
@@ -16904,8 +17087,11 @@
       <c r="C61" s="4" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D61" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>346</v>
       </c>
@@ -16915,8 +17101,11 @@
       <c r="C62" s="4" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D62" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>346</v>
       </c>
@@ -16926,8 +17115,11 @@
       <c r="C63" s="4" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D63" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>346</v>
       </c>
@@ -16937,8 +17129,11 @@
       <c r="C64" s="4" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D64" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>346</v>
       </c>
@@ -16948,8 +17143,11 @@
       <c r="C65" s="4" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D65" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>346</v>
       </c>
@@ -16959,8 +17157,11 @@
       <c r="C66" s="4" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D66" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>346</v>
       </c>
@@ -16970,8 +17171,11 @@
       <c r="C67" s="4" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D67" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>346</v>
       </c>
@@ -16981,8 +17185,11 @@
       <c r="C68" s="4" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D68" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>346</v>
       </c>
@@ -16992,8 +17199,11 @@
       <c r="C69" s="4" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D69" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>346</v>
       </c>
@@ -17003,8 +17213,11 @@
       <c r="C70" s="4" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D70" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>346</v>
       </c>
@@ -17014,8 +17227,11 @@
       <c r="C71" s="4" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D71" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>346</v>
       </c>
@@ -17025,8 +17241,11 @@
       <c r="C72" s="4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D72" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>346</v>
       </c>
@@ -17036,8 +17255,11 @@
       <c r="C73" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D73" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>346</v>
       </c>
@@ -17047,8 +17269,11 @@
       <c r="C74" s="4" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D74" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>346</v>
       </c>
@@ -17058,8 +17283,11 @@
       <c r="C75" s="4" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D75" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>346</v>
       </c>
@@ -17069,8 +17297,11 @@
       <c r="C76" s="4" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D76" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>346</v>
       </c>
@@ -17080,8 +17311,11 @@
       <c r="C77" s="4" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D77" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>346</v>
       </c>
@@ -17091,8 +17325,11 @@
       <c r="C78" s="4" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D78" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>346</v>
       </c>
@@ -17102,8 +17339,11 @@
       <c r="C79" s="4" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D79" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>346</v>
       </c>
@@ -17113,8 +17353,11 @@
       <c r="C80" s="4" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D80" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>346</v>
       </c>
@@ -17124,8 +17367,11 @@
       <c r="C81" s="4" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D81" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>346</v>
       </c>
@@ -17135,8 +17381,11 @@
       <c r="C82" s="4" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D82" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>346</v>
       </c>
@@ -17146,8 +17395,11 @@
       <c r="C83" s="4" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D83" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>346</v>
       </c>
@@ -17157,8 +17409,11 @@
       <c r="C84" s="4" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D84" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>346</v>
       </c>
@@ -17168,8 +17423,11 @@
       <c r="C85" s="4" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D85" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>346</v>
       </c>
@@ -17179,8 +17437,11 @@
       <c r="C86" s="4" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D86" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>346</v>
       </c>
@@ -17190,8 +17451,11 @@
       <c r="C87" s="4" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D87" s="3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>346</v>
       </c>
@@ -17201,8 +17465,11 @@
       <c r="C88" s="4" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D88" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>346</v>
       </c>
@@ -17212,8 +17479,11 @@
       <c r="C89" s="4" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D89" s="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>346</v>
       </c>
@@ -17223,8 +17493,11 @@
       <c r="C90" s="4" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D90" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>346</v>
       </c>
@@ -17234,8 +17507,11 @@
       <c r="C91" s="4" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D91" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>346</v>
       </c>
@@ -17245,8 +17521,11 @@
       <c r="C92" s="4" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D92" s="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>346</v>
       </c>
@@ -17256,8 +17535,11 @@
       <c r="C93" s="4" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D93" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>346</v>
       </c>
@@ -17267,8 +17549,11 @@
       <c r="C94" s="4" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D94" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>346</v>
       </c>
@@ -17278,8 +17563,11 @@
       <c r="C95" s="4" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D95" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>346</v>
       </c>
@@ -17289,8 +17577,11 @@
       <c r="C96" s="4" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D96" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>346</v>
       </c>
@@ -17300,8 +17591,11 @@
       <c r="C97" s="4" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D97" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>346</v>
       </c>
@@ -17311,8 +17605,11 @@
       <c r="C98" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D98" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>346</v>
       </c>
@@ -17322,8 +17619,11 @@
       <c r="C99" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D99" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>346</v>
       </c>
@@ -17333,8 +17633,11 @@
       <c r="C100" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D100" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>346</v>
       </c>
@@ -17344,8 +17647,11 @@
       <c r="C101" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>346</v>
       </c>
@@ -17355,8 +17661,11 @@
       <c r="C102" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D102" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>346</v>
       </c>
@@ -17366,8 +17675,11 @@
       <c r="C103" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D103" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>346</v>
       </c>
@@ -17375,8 +17687,11 @@
       <c r="C104" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D104" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>346</v>
       </c>
@@ -17384,8 +17699,11 @@
       <c r="C105" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D105" s="3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>346</v>
       </c>
@@ -17393,8 +17711,11 @@
       <c r="C106" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D106" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>346</v>
       </c>
@@ -17402,8 +17723,11 @@
       <c r="C107" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D107" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>346</v>
       </c>
@@ -17411,8 +17735,11 @@
       <c r="C108" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D108" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>346</v>
       </c>
@@ -17420,14 +17747,20 @@
       <c r="C109" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D109" s="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>346</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="4" t="s">
         <v>41</v>
+      </c>
+      <c r="D110" s="3">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -17439,14 +17772,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -17456,8 +17790,13 @@
       <c r="C1" s="2" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17473,8 +17812,11 @@
           <t>BKM</t>
         </is>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17490,8 +17832,11 @@
           <t>CAM</t>
         </is>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17507,8 +17852,11 @@
           <t>CMA</t>
         </is>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17524,8 +17872,11 @@
           <t>DBY</t>
         </is>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17541,8 +17892,11 @@
           <t>DEV</t>
         </is>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17558,8 +17912,11 @@
           <t>DOR</t>
         </is>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17575,8 +17932,11 @@
           <t>ESX</t>
         </is>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17592,8 +17952,11 @@
           <t>ESS</t>
         </is>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17609,8 +17972,11 @@
           <t>GLS</t>
         </is>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17626,8 +17992,11 @@
           <t>HAM</t>
         </is>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17643,8 +18012,11 @@
           <t>HRT</t>
         </is>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17660,8 +18032,11 @@
           <t>KEN</t>
         </is>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17677,8 +18052,11 @@
           <t>LAN</t>
         </is>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17694,8 +18072,11 @@
           <t>LEC</t>
         </is>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17711,8 +18092,11 @@
           <t>LIN</t>
         </is>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17728,8 +18112,11 @@
           <t>NFK</t>
         </is>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17745,8 +18132,11 @@
           <t>NYK</t>
         </is>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17762,8 +18152,11 @@
           <t>NTH</t>
         </is>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17779,8 +18172,11 @@
           <t>NTT</t>
         </is>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17796,8 +18192,11 @@
           <t>OXF</t>
         </is>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17813,8 +18212,11 @@
           <t>SOM</t>
         </is>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17830,8 +18232,11 @@
           <t>STS</t>
         </is>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17847,8 +18252,11 @@
           <t>SFK</t>
         </is>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17864,8 +18272,11 @@
           <t>SRY</t>
         </is>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17881,8 +18292,11 @@
           <t>WAR</t>
         </is>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17898,8 +18312,11 @@
           <t>WSX</t>
         </is>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17915,8 +18332,11 @@
           <t>WOR</t>
         </is>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17932,8 +18352,11 @@
           <t>BDG</t>
         </is>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17949,8 +18372,11 @@
           <t>BNE</t>
         </is>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17966,8 +18392,11 @@
           <t>BEX</t>
         </is>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -17983,8 +18412,11 @@
           <t>BEN</t>
         </is>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D32" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18000,8 +18432,11 @@
           <t>BRY</t>
         </is>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D33" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18017,8 +18452,11 @@
           <t>CMD</t>
         </is>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D34" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18034,8 +18472,11 @@
           <t>CRY</t>
         </is>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18051,8 +18492,11 @@
           <t>EAL</t>
         </is>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D36" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18068,8 +18512,11 @@
           <t>ENF</t>
         </is>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18085,8 +18532,11 @@
           <t>GRE</t>
         </is>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18102,8 +18552,11 @@
           <t>HCK</t>
         </is>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18119,8 +18572,11 @@
           <t>HMF</t>
         </is>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18136,8 +18592,11 @@
           <t>HRY</t>
         </is>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18153,8 +18612,11 @@
           <t>HRW</t>
         </is>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D42" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18170,8 +18632,11 @@
           <t>HAV</t>
         </is>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D43" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18187,8 +18652,11 @@
           <t>HIL</t>
         </is>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D44" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18204,8 +18672,11 @@
           <t>HNS</t>
         </is>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18221,8 +18692,11 @@
           <t>ISL</t>
         </is>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D46" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18238,8 +18712,11 @@
           <t>KEC</t>
         </is>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D47" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18255,8 +18732,11 @@
           <t>KTT</t>
         </is>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D48" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18272,8 +18752,11 @@
           <t>LBH</t>
         </is>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18289,8 +18772,11 @@
           <t>LEW</t>
         </is>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D50" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18306,8 +18792,11 @@
           <t>MRT</t>
         </is>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D51" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18323,8 +18812,11 @@
           <t>NWM</t>
         </is>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D52" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18340,8 +18832,11 @@
           <t>RDB</t>
         </is>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D53" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18357,8 +18852,11 @@
           <t>RIC</t>
         </is>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D54" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18374,8 +18872,11 @@
           <t>SWK</t>
         </is>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D55" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18391,8 +18892,11 @@
           <t>STN</t>
         </is>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D56" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18408,8 +18912,11 @@
           <t>TWH</t>
         </is>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18425,8 +18932,11 @@
           <t>WFT</t>
         </is>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D58" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18442,8 +18952,11 @@
           <t>WND</t>
         </is>
       </c>
-    </row>
-    <row r="60" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D59" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18459,8 +18972,11 @@
           <t>WSM</t>
         </is>
       </c>
-    </row>
-    <row r="61" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D60" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18476,8 +18992,11 @@
           <t>BNS</t>
         </is>
       </c>
-    </row>
-    <row r="62" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D61" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18493,8 +19012,11 @@
           <t>BIR</t>
         </is>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D62" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18510,8 +19032,11 @@
           <t>BOL</t>
         </is>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D63" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18527,8 +19052,11 @@
           <t>BRD</t>
         </is>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D64" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18544,8 +19072,11 @@
           <t>BUR</t>
         </is>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D65" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18561,8 +19092,11 @@
           <t>CLD</t>
         </is>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D66" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18578,8 +19112,11 @@
           <t>COV</t>
         </is>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D67" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18595,8 +19132,11 @@
           <t>DNC</t>
         </is>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D68" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18612,8 +19152,11 @@
           <t>DUD</t>
         </is>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D69" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18629,8 +19172,11 @@
           <t>GAT</t>
         </is>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D70" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18646,8 +19192,11 @@
           <t>KIR</t>
         </is>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D71" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18663,8 +19212,11 @@
           <t>KWL</t>
         </is>
       </c>
-    </row>
-    <row r="73" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D72" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18680,8 +19232,11 @@
           <t>LDS</t>
         </is>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D73" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18697,8 +19252,11 @@
           <t>LIV</t>
         </is>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D74" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18714,8 +19272,11 @@
           <t>MAN</t>
         </is>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D75" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18731,8 +19292,11 @@
           <t>NET</t>
         </is>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D76" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18748,8 +19312,11 @@
           <t>NTY</t>
         </is>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D77" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18765,8 +19332,11 @@
           <t>OLD</t>
         </is>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D78" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18782,8 +19352,11 @@
           <t>RCH</t>
         </is>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D79" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18799,8 +19372,11 @@
           <t>ROT</t>
         </is>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D80" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18816,8 +19392,11 @@
           <t>SHN</t>
         </is>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D81" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18833,8 +19412,11 @@
           <t>SLF</t>
         </is>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D82" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18850,8 +19432,11 @@
           <t>SAW</t>
         </is>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D83" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18867,8 +19452,11 @@
           <t>SFT</t>
         </is>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D84" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18884,8 +19472,11 @@
           <t>SHF</t>
         </is>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D85" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18901,8 +19492,11 @@
           <t>SOL</t>
         </is>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D86" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18918,8 +19512,11 @@
           <t>STY</t>
         </is>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D87" s="3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18935,8 +19532,11 @@
           <t>SKP</t>
         </is>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D88" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18952,8 +19552,11 @@
           <t>SND</t>
         </is>
       </c>
-    </row>
-    <row r="90" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D89" s="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18969,8 +19572,11 @@
           <t>TAM</t>
         </is>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D90" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -18986,8 +19592,11 @@
           <t>TRF</t>
         </is>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D91" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19003,8 +19612,11 @@
           <t>WKF</t>
         </is>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D92" s="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19020,8 +19632,11 @@
           <t>WLL</t>
         </is>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D93" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19037,8 +19652,11 @@
           <t>WGN</t>
         </is>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D94" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19054,8 +19672,11 @@
           <t>WRL</t>
         </is>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D95" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19071,8 +19692,11 @@
           <t>WLV</t>
         </is>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D96" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19088,8 +19712,11 @@
           <t>BAS</t>
         </is>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D97" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19105,8 +19732,11 @@
           <t>BBD</t>
         </is>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D98" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19122,8 +19752,11 @@
           <t>BDF</t>
         </is>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D99" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19139,8 +19772,11 @@
           <t>BPL</t>
         </is>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D100" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19156,8 +19792,11 @@
           <t>BMH</t>
         </is>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19173,8 +19812,11 @@
           <t>BRC</t>
         </is>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D102" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19190,8 +19832,11 @@
           <t>BNH</t>
         </is>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D103" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19207,8 +19852,11 @@
           <t>BST</t>
         </is>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D104" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19224,8 +19872,11 @@
           <t>CBF</t>
         </is>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D105" s="3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19241,8 +19892,11 @@
           <t>CHE</t>
         </is>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D106" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19258,8 +19912,11 @@
           <t>CHW</t>
         </is>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D107" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19275,8 +19932,11 @@
           <t>CON</t>
         </is>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D108" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19292,8 +19952,11 @@
           <t>DAL</t>
         </is>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D109" s="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19309,8 +19972,11 @@
           <t>DER</t>
         </is>
       </c>
-    </row>
-    <row r="111" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D110" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19326,8 +19992,11 @@
           <t>DUR</t>
         </is>
       </c>
-    </row>
-    <row r="112" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D111" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19343,8 +20012,11 @@
           <t>ERY</t>
         </is>
       </c>
-    </row>
-    <row r="113" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D112" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19360,8 +20032,11 @@
           <t>HAL</t>
         </is>
       </c>
-    </row>
-    <row r="114" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D113" s="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19377,8 +20052,11 @@
           <t>HPL</t>
         </is>
       </c>
-    </row>
-    <row r="115" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D114" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19394,8 +20072,11 @@
           <t>HEF</t>
         </is>
       </c>
-    </row>
-    <row r="116" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D115" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19411,8 +20092,11 @@
           <t>IOW</t>
         </is>
       </c>
-    </row>
-    <row r="117" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D116" s="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19428,8 +20112,11 @@
           <t>KHL</t>
         </is>
       </c>
-    </row>
-    <row r="118" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D117" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19445,8 +20132,11 @@
           <t>LCE</t>
         </is>
       </c>
-    </row>
-    <row r="119" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D118" s="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19462,8 +20152,11 @@
           <t>LUT</t>
         </is>
       </c>
-    </row>
-    <row r="120" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D119" s="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19479,8 +20172,11 @@
           <t>MDB</t>
         </is>
       </c>
-    </row>
-    <row r="121" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D120" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19496,8 +20192,11 @@
           <t>MIK</t>
         </is>
       </c>
-    </row>
-    <row r="122" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D121" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19513,8 +20212,11 @@
           <t>NEL</t>
         </is>
       </c>
-    </row>
-    <row r="123" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D122" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19530,8 +20232,11 @@
           <t>NLN</t>
         </is>
       </c>
-    </row>
-    <row r="124" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D123" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19547,8 +20252,11 @@
           <t>NSM</t>
         </is>
       </c>
-    </row>
-    <row r="125" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D124" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19564,8 +20272,11 @@
           <t>NBL</t>
         </is>
       </c>
-    </row>
-    <row r="126" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D125" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19581,8 +20292,11 @@
           <t>NGM</t>
         </is>
       </c>
-    </row>
-    <row r="127" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D126" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19598,8 +20312,11 @@
           <t>PTE</t>
         </is>
       </c>
-    </row>
-    <row r="128" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D127" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19615,8 +20332,11 @@
           <t>PLY</t>
         </is>
       </c>
-    </row>
-    <row r="129" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D128" s="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19632,8 +20352,11 @@
           <t>POL</t>
         </is>
       </c>
-    </row>
-    <row r="130" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D129" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19649,8 +20372,11 @@
           <t>POR</t>
         </is>
       </c>
-    </row>
-    <row r="131" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D130" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19666,8 +20392,11 @@
           <t>RDG</t>
         </is>
       </c>
-    </row>
-    <row r="132" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D131" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19683,8 +20412,11 @@
           <t>RCC</t>
         </is>
       </c>
-    </row>
-    <row r="133" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D132" s="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19700,8 +20432,11 @@
           <t>RUT</t>
         </is>
       </c>
-    </row>
-    <row r="134" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D133" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19717,8 +20452,11 @@
           <t>SHR</t>
         </is>
       </c>
-    </row>
-    <row r="135" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D134" s="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19734,8 +20472,11 @@
           <t>SLG</t>
         </is>
       </c>
-    </row>
-    <row r="136" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D135" s="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19751,8 +20492,11 @@
           <t>SGC</t>
         </is>
       </c>
-    </row>
-    <row r="137" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D136" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19768,8 +20512,11 @@
           <t>STH</t>
         </is>
       </c>
-    </row>
-    <row r="138" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D137" s="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19785,8 +20532,11 @@
           <t>SOS</t>
         </is>
       </c>
-    </row>
-    <row r="139" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D138" s="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19802,8 +20552,11 @@
           <t>STT</t>
         </is>
       </c>
-    </row>
-    <row r="140" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D139" s="3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19819,8 +20572,11 @@
           <t>STE</t>
         </is>
       </c>
-    </row>
-    <row r="141" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D140" s="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19836,8 +20592,11 @@
           <t>SWD</t>
         </is>
       </c>
-    </row>
-    <row r="142" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D141" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19853,8 +20612,11 @@
           <t>TFW</t>
         </is>
       </c>
-    </row>
-    <row r="143" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D142" s="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19870,8 +20632,11 @@
           <t>THR</t>
         </is>
       </c>
-    </row>
-    <row r="144" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D143" s="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19887,8 +20652,11 @@
           <t>TOB</t>
         </is>
       </c>
-    </row>
-    <row r="145" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D144" s="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19904,8 +20672,11 @@
           <t>WRT</t>
         </is>
       </c>
-    </row>
-    <row r="146" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D145" s="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19921,8 +20692,11 @@
           <t>WBK</t>
         </is>
       </c>
-    </row>
-    <row r="147" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D146" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19938,8 +20712,11 @@
           <t>WIL</t>
         </is>
       </c>
-    </row>
-    <row r="148" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D147" s="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19955,8 +20732,11 @@
           <t>WNM</t>
         </is>
       </c>
-    </row>
-    <row r="149" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D148" s="3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19972,8 +20752,11 @@
           <t>WOK</t>
         </is>
       </c>
-    </row>
-    <row r="150" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D149" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -19989,8 +20772,11 @@
           <t>YOR</t>
         </is>
       </c>
-    </row>
-    <row r="151" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D150" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20006,8 +20792,11 @@
           <t>LND</t>
         </is>
       </c>
-    </row>
-    <row r="152" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D151" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20023,8 +20812,11 @@
           <t>ANT</t>
         </is>
       </c>
-    </row>
-    <row r="153" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D152" s="3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20040,8 +20832,11 @@
           <t>ARD</t>
         </is>
       </c>
-    </row>
-    <row r="154" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D153" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20057,8 +20852,11 @@
           <t>ARM</t>
         </is>
       </c>
-    </row>
-    <row r="155" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D154" s="3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20074,8 +20872,11 @@
           <t>BLA</t>
         </is>
       </c>
-    </row>
-    <row r="156" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D155" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20091,8 +20892,11 @@
           <t>BLY</t>
         </is>
       </c>
-    </row>
-    <row r="157" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D156" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20108,8 +20912,11 @@
           <t>BNB</t>
         </is>
       </c>
-    </row>
-    <row r="158" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D157" s="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20125,8 +20932,11 @@
           <t>BFS</t>
         </is>
       </c>
-    </row>
-    <row r="159" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D158" s="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20142,8 +20952,11 @@
           <t>CKF</t>
         </is>
       </c>
-    </row>
-    <row r="160" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D159" s="3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20159,8 +20972,11 @@
           <t>CSR</t>
         </is>
       </c>
-    </row>
-    <row r="161" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D160" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20176,8 +20992,11 @@
           <t>CLR</t>
         </is>
       </c>
-    </row>
-    <row r="162" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D161" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20193,8 +21012,11 @@
           <t>CKT</t>
         </is>
       </c>
-    </row>
-    <row r="163" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D162" s="3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20210,8 +21032,11 @@
           <t>CGV</t>
         </is>
       </c>
-    </row>
-    <row r="164" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D163" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20227,8 +21052,11 @@
           <t>DRY</t>
         </is>
       </c>
-    </row>
-    <row r="165" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D164" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20244,8 +21072,11 @@
           <t>DOW</t>
         </is>
       </c>
-    </row>
-    <row r="166" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D165" s="3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20261,8 +21092,11 @@
           <t>DGN</t>
         </is>
       </c>
-    </row>
-    <row r="167" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D166" s="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20278,8 +21112,11 @@
           <t>FER</t>
         </is>
       </c>
-    </row>
-    <row r="168" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D167" s="3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20295,8 +21132,11 @@
           <t>LRN</t>
         </is>
       </c>
-    </row>
-    <row r="169" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D168" s="3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20312,8 +21152,11 @@
           <t>LMV</t>
         </is>
       </c>
-    </row>
-    <row r="170" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D169" s="3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20329,8 +21172,11 @@
           <t>LSB</t>
         </is>
       </c>
-    </row>
-    <row r="171" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D170" s="3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20346,8 +21192,11 @@
           <t>MFT</t>
         </is>
       </c>
-    </row>
-    <row r="172" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D171" s="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20363,8 +21212,11 @@
           <t>MYL</t>
         </is>
       </c>
-    </row>
-    <row r="173" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D172" s="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20380,8 +21232,11 @@
           <t>NYM</t>
         </is>
       </c>
-    </row>
-    <row r="174" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D173" s="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20397,8 +21252,11 @@
           <t>NTA</t>
         </is>
       </c>
-    </row>
-    <row r="175" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D174" s="3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20414,8 +21272,11 @@
           <t>NDN</t>
         </is>
       </c>
-    </row>
-    <row r="176" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D175" s="3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20431,8 +21292,11 @@
           <t>OMH</t>
         </is>
       </c>
-    </row>
-    <row r="177" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D176" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20448,8 +21312,11 @@
           <t>STB</t>
         </is>
       </c>
-    </row>
-    <row r="178" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D177" s="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20465,8 +21332,11 @@
           <t>ABE</t>
         </is>
       </c>
-    </row>
-    <row r="179" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D178" s="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20482,8 +21352,11 @@
           <t>ABD</t>
         </is>
       </c>
-    </row>
-    <row r="180" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D179" s="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20499,8 +21372,11 @@
           <t>ANS</t>
         </is>
       </c>
-    </row>
-    <row r="181" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D180" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20516,8 +21392,11 @@
           <t>AGB</t>
         </is>
       </c>
-    </row>
-    <row r="182" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D181" s="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20533,8 +21412,11 @@
           <t>CLK</t>
         </is>
       </c>
-    </row>
-    <row r="183" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D182" s="3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20550,8 +21432,11 @@
           <t>DGY</t>
         </is>
       </c>
-    </row>
-    <row r="184" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D183" s="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20567,8 +21452,11 @@
           <t>DND</t>
         </is>
       </c>
-    </row>
-    <row r="185" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D184" s="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20584,8 +21472,11 @@
           <t>EAY</t>
         </is>
       </c>
-    </row>
-    <row r="186" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D185" s="3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20601,8 +21492,11 @@
           <t>EDU</t>
         </is>
       </c>
-    </row>
-    <row r="187" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D186" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20618,8 +21512,11 @@
           <t>ELN</t>
         </is>
       </c>
-    </row>
-    <row r="188" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D187" s="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20635,8 +21532,11 @@
           <t>ERW</t>
         </is>
       </c>
-    </row>
-    <row r="189" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D188" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20652,8 +21552,11 @@
           <t>EDH</t>
         </is>
       </c>
-    </row>
-    <row r="190" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D189" s="3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20669,8 +21572,11 @@
           <t>ELS</t>
         </is>
       </c>
-    </row>
-    <row r="191" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D190" s="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20686,8 +21592,11 @@
           <t>FAL</t>
         </is>
       </c>
-    </row>
-    <row r="192" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D191" s="3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20703,8 +21612,11 @@
           <t>FIF</t>
         </is>
       </c>
-    </row>
-    <row r="193" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D192" s="3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20720,8 +21632,11 @@
           <t>GLG</t>
         </is>
       </c>
-    </row>
-    <row r="194" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D193" s="3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20737,8 +21652,11 @@
           <t>HLD</t>
         </is>
       </c>
-    </row>
-    <row r="195" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D194" s="3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20754,8 +21672,11 @@
           <t>IVC</t>
         </is>
       </c>
-    </row>
-    <row r="196" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D195" s="3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20771,8 +21692,11 @@
           <t>MLN</t>
         </is>
       </c>
-    </row>
-    <row r="197" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D196" s="3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20788,8 +21712,11 @@
           <t>MRY</t>
         </is>
       </c>
-    </row>
-    <row r="198" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D197" s="3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20805,8 +21732,11 @@
           <t>NAY</t>
         </is>
       </c>
-    </row>
-    <row r="199" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D198" s="3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20822,8 +21752,11 @@
           <t>NLK</t>
         </is>
       </c>
-    </row>
-    <row r="200" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D199" s="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20839,8 +21772,11 @@
           <t>ORK</t>
         </is>
       </c>
-    </row>
-    <row r="201" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D200" s="3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20856,8 +21792,11 @@
           <t>PKN</t>
         </is>
       </c>
-    </row>
-    <row r="202" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D201" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20873,8 +21812,11 @@
           <t>RFW</t>
         </is>
       </c>
-    </row>
-    <row r="203" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D202" s="3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20890,8 +21832,11 @@
           <t>SCB</t>
         </is>
       </c>
-    </row>
-    <row r="204" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D203" s="3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20907,8 +21852,11 @@
           <t>ZET</t>
         </is>
       </c>
-    </row>
-    <row r="205" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D204" s="3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20924,8 +21872,11 @@
           <t>SAY</t>
         </is>
       </c>
-    </row>
-    <row r="206" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D205" s="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20941,8 +21892,11 @@
           <t>SLK</t>
         </is>
       </c>
-    </row>
-    <row r="207" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D206" s="3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20958,8 +21912,11 @@
           <t>STG</t>
         </is>
       </c>
-    </row>
-    <row r="208" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D207" s="3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20975,8 +21932,11 @@
           <t>WDU</t>
         </is>
       </c>
-    </row>
-    <row r="209" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D208" s="3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -20992,8 +21952,11 @@
           <t>WLN</t>
         </is>
       </c>
-    </row>
-    <row r="210" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D209" s="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21009,8 +21972,11 @@
           <t>BGW</t>
         </is>
       </c>
-    </row>
-    <row r="211" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D210" s="3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21026,8 +21992,11 @@
           <t>BGE</t>
         </is>
       </c>
-    </row>
-    <row r="212" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D211" s="3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21043,8 +22012,11 @@
           <t>CRF</t>
         </is>
       </c>
-    </row>
-    <row r="213" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D212" s="3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21060,8 +22032,11 @@
           <t>CMN</t>
         </is>
       </c>
-    </row>
-    <row r="214" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D213" s="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21077,8 +22052,11 @@
           <t>CGN</t>
         </is>
       </c>
-    </row>
-    <row r="215" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D214" s="3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21094,8 +22072,11 @@
           <t>DEN</t>
         </is>
       </c>
-    </row>
-    <row r="216" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D215" s="3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21111,8 +22092,11 @@
           <t>FLN</t>
         </is>
       </c>
-    </row>
-    <row r="217" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D216" s="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21128,8 +22112,11 @@
           <t>GWN</t>
         </is>
       </c>
-    </row>
-    <row r="218" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D217" s="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21145,8 +22132,11 @@
           <t>AGY</t>
         </is>
       </c>
-    </row>
-    <row r="219" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D218" s="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21162,8 +22152,11 @@
           <t>MTY</t>
         </is>
       </c>
-    </row>
-    <row r="220" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D219" s="3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21175,8 +22168,11 @@
           <t>MDW</t>
         </is>
       </c>
-    </row>
-    <row r="221" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D220" s="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21188,8 +22184,11 @@
           <t>CAY</t>
         </is>
       </c>
-    </row>
-    <row r="222" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D221" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -21200,6 +22199,9 @@
         <is>
           <t>CWY</t>
         </is>
+      </c>
+      <c r="D222" s="3">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/doc/state_mapping.xlsx
+++ b/doc/state_mapping.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="France T005S Map" sheetId="2" r:id="rId2"/>
     <sheet name="GB T005S Map" sheetId="3" r:id="rId6"/>
+    <sheet name="Germany T005S Map" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -22207,4 +22208,355 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>HH</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>BY</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>MV</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/state_mapping.xlsx
+++ b/doc/state_mapping.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wudaoyou/Dev/git/boc/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B365092A-B8EB-D74F-BDA3-306830D50E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1C6279-1586-DF46-B347-B8B2B6A0A350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="France T005S Map" sheetId="2" r:id="rId2"/>
-    <sheet name="GB T005S Map" sheetId="3" r:id="rId6"/>
-    <sheet name="Germany T005S Map" sheetId="4" r:id="rId7"/>
+    <sheet name="GB T005S Map" sheetId="3" r:id="rId3"/>
+    <sheet name="Germany T005S Map" sheetId="4" r:id="rId4"/>
+    <sheet name="Austria T005S Map" sheetId="5" r:id="rId5"/>
+    <sheet name="China T005S Map" sheetId="6" r:id="rId6"/>
+    <sheet name="Spain T005S Map" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="1036">
   <si>
     <t>[OPERATOR]</t>
   </si>
@@ -2742,6 +2745,417 @@
   </si>
   <si>
     <t>Merthyr Tydfil</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>HA</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>YN</t>
+  </si>
+  <si>
+    <t>OX</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>HW</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>YS</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>YW</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>BF</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>DU</t>
+  </si>
+  <si>
+    <t>ER</t>
+  </si>
+  <si>
+    <t>HL</t>
+  </si>
+  <si>
+    <t>IW</t>
+  </si>
+  <si>
+    <t>KH</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>LU</t>
+  </si>
+  <si>
+    <t>MK</t>
+  </si>
+  <si>
+    <t>NS</t>
+  </si>
+  <si>
+    <t>NU</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>WR</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>BK</t>
+  </si>
+  <si>
+    <t>WO</t>
+  </si>
+  <si>
+    <t>YK</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>WL</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>BO</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>DY</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>GY</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>NW</t>
+  </si>
+  <si>
+    <t>HE</t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>NÖ</t>
+  </si>
+  <si>
+    <t>OÖ</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
 </sst>
 </file>
@@ -2913,6 +3327,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B72B8BE2-88D9-C475-E771-57A506196C41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -3117,7 +3585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130DE18E-7BAC-4047-A454-69BF09887E2F}">
   <dimension ref="A1:N409"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -16227,7 +16695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3447E385-6E30-2F4A-8B4C-5328F4B9E411}">
   <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16246,10 +16714,8 @@
       <c r="C1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17772,7 +18238,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D92772C-FCC0-9F4F-B254-1C7078C6A5A1}">
   <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -17791,4415 +18257,3093 @@
       <c r="C1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>BU</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>BKM</t>
-        </is>
+      <c r="A2" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>457</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>CAM</t>
-        </is>
+      <c r="A3" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>459</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
+      <c r="A4" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>461</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>DBY</t>
-        </is>
+      <c r="A5" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>DV</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>DEV</t>
-        </is>
+      <c r="A6" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>465</v>
       </c>
       <c r="D6" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>DOR</t>
-        </is>
+      <c r="A7" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>ESX</t>
-        </is>
+      <c r="A8" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>469</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>ESS</t>
-        </is>
+      <c r="A9" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="D9" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
+      <c r="A10" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="D10" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>HA</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>HAM</t>
-        </is>
+      <c r="A11" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>HRT</t>
-        </is>
+      <c r="A12" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="D12" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>KE</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>KEN</t>
-        </is>
+      <c r="A13" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="D13" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
+      <c r="A14" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>481</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
+      <c r="A15" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="D15" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
+      <c r="A16" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>485</v>
       </c>
       <c r="D16" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>NK</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>NFK</t>
-        </is>
+      <c r="A17" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>487</v>
       </c>
       <c r="D17" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>YN</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
+      <c r="A18" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>489</v>
       </c>
       <c r="D18" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>NTH</t>
-        </is>
+      <c r="A19" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>491</v>
       </c>
       <c r="D19" s="3">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
+      <c r="A20" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>493</v>
       </c>
       <c r="D20" s="3">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>OX</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>OXF</t>
-        </is>
+      <c r="A21" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>495</v>
       </c>
       <c r="D21" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>SOM</t>
-        </is>
+      <c r="A22" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>497</v>
       </c>
       <c r="D22" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>STS</t>
-        </is>
+      <c r="A23" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D23" s="3">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>SFK</t>
-        </is>
+      <c r="A24" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>501</v>
       </c>
       <c r="D24" s="3">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>SY</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>SRY</t>
-        </is>
+      <c r="A25" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="D25" s="3">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>WAR</t>
-        </is>
+      <c r="A26" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>505</v>
       </c>
       <c r="D26" s="3">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>WSX</t>
-        </is>
+      <c r="A27" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>507</v>
       </c>
       <c r="D27" s="3">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>HW</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>WOR</t>
-        </is>
+      <c r="A28" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>509</v>
       </c>
       <c r="D28" s="3">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>BDG</t>
-        </is>
+      <c r="A29" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>511</v>
       </c>
       <c r="D29" s="3">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>BNE</t>
-        </is>
+      <c r="A30" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>513</v>
       </c>
       <c r="D30" s="3">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>BEX</t>
-        </is>
+      <c r="A31" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>515</v>
       </c>
       <c r="D31" s="3">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
+      <c r="A32" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>517</v>
       </c>
       <c r="D32" s="3">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>BRY</t>
-        </is>
+      <c r="A33" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>519</v>
       </c>
       <c r="D33" s="3">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>CMD</t>
-        </is>
+      <c r="A34" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>521</v>
       </c>
       <c r="D34" s="3">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>CRY</t>
-        </is>
+      <c r="A35" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>523</v>
       </c>
       <c r="D35" s="3">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>EAL</t>
-        </is>
+      <c r="A36" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>525</v>
       </c>
       <c r="D36" s="3">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>ENF</t>
-        </is>
+      <c r="A37" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>527</v>
       </c>
       <c r="D37" s="3">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>GRE</t>
-        </is>
+      <c r="A38" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>529</v>
       </c>
       <c r="D38" s="3">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>HCK</t>
-        </is>
+      <c r="A39" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>531</v>
       </c>
       <c r="D39" s="3">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>HMF</t>
-        </is>
+      <c r="A40" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>533</v>
       </c>
       <c r="D40" s="3">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>HRY</t>
-        </is>
+      <c r="A41" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>535</v>
       </c>
       <c r="D41" s="3">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>HRW</t>
-        </is>
+      <c r="A42" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>537</v>
       </c>
       <c r="D42" s="3">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>HAV</t>
-        </is>
+      <c r="A43" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>539</v>
       </c>
       <c r="D43" s="3">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>HIL</t>
-        </is>
+      <c r="A44" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>541</v>
       </c>
       <c r="D44" s="3">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>HNS</t>
-        </is>
+      <c r="A45" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>543</v>
       </c>
       <c r="D45" s="3">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>ISL</t>
-        </is>
+      <c r="A46" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>545</v>
       </c>
       <c r="D46" s="3">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>KEC</t>
-        </is>
+      <c r="A47" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>547</v>
       </c>
       <c r="D47" s="3">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>KTT</t>
-        </is>
+      <c r="A48" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>549</v>
       </c>
       <c r="D48" s="3">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>LBH</t>
-        </is>
+      <c r="A49" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>551</v>
       </c>
       <c r="D49" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>LEW</t>
-        </is>
+      <c r="A50" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>553</v>
       </c>
       <c r="D50" s="3">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>MRT</t>
-        </is>
+      <c r="A51" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>555</v>
       </c>
       <c r="D51" s="3">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>NWM</t>
-        </is>
+      <c r="A52" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>557</v>
       </c>
       <c r="D52" s="3">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>RDB</t>
-        </is>
+      <c r="A53" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>559</v>
       </c>
       <c r="D53" s="3">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>RIC</t>
-        </is>
+      <c r="A54" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>561</v>
       </c>
       <c r="D54" s="3">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
+      <c r="A55" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>563</v>
       </c>
       <c r="D55" s="3">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>STN</t>
-        </is>
+      <c r="A56" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>565</v>
       </c>
       <c r="D56" s="3">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>TWH</t>
-        </is>
+      <c r="A57" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>567</v>
       </c>
       <c r="D57" s="3">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>WFT</t>
-        </is>
+      <c r="A58" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>569</v>
       </c>
       <c r="D58" s="3">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>WND</t>
-        </is>
+      <c r="A59" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>571</v>
       </c>
       <c r="D59" s="3">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>WSM</t>
-        </is>
+      <c r="A60" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>573</v>
       </c>
       <c r="D60" s="3">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>YS</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>BNS</t>
-        </is>
+      <c r="A61" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>575</v>
       </c>
       <c r="D61" s="3">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
+      <c r="A62" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>577</v>
       </c>
       <c r="D62" s="3">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
+      <c r="A63" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>579</v>
       </c>
       <c r="D63" s="3">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>YW</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>BRD</t>
-        </is>
+      <c r="A64" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>581</v>
       </c>
       <c r="D64" s="3">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>BUR</t>
-        </is>
+      <c r="A65" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="D65" s="3">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>YW</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>CLD</t>
-        </is>
+      <c r="A66" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>585</v>
       </c>
       <c r="D66" s="3">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>COV</t>
-        </is>
+      <c r="A67" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="D67" s="3">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>YS</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>DNC</t>
-        </is>
+      <c r="A68" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>589</v>
       </c>
       <c r="D68" s="3">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>DUD</t>
-        </is>
+      <c r="A69" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="D69" s="3">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>GAT</t>
-        </is>
+      <c r="A70" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="D70" s="3">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>YW</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>KIR</t>
-        </is>
+      <c r="A71" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>595</v>
       </c>
       <c r="D71" s="3">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>KWL</t>
-        </is>
+      <c r="A72" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="D72" s="3">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>YW</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>LDS</t>
-        </is>
+      <c r="A73" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>599</v>
       </c>
       <c r="D73" s="3">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>LIV</t>
-        </is>
+      <c r="A74" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="D74" s="3">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>MAN</t>
-        </is>
+      <c r="A75" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>603</v>
       </c>
       <c r="D75" s="3">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
+      <c r="A76" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>605</v>
       </c>
       <c r="D76" s="3">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>NTY</t>
-        </is>
+      <c r="A77" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>607</v>
       </c>
       <c r="D77" s="3">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
+      <c r="A78" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>609</v>
       </c>
       <c r="D78" s="3">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>RCH</t>
-        </is>
+      <c r="A79" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>611</v>
       </c>
       <c r="D79" s="3">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>YS</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>ROT</t>
-        </is>
+      <c r="A80" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="D80" s="3">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>SHN</t>
-        </is>
+      <c r="A81" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>615</v>
       </c>
       <c r="D81" s="3">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
+      <c r="A82" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>617</v>
       </c>
       <c r="D82" s="3">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>SAW</t>
-        </is>
+      <c r="A83" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>619</v>
       </c>
       <c r="D83" s="3">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>SFT</t>
-        </is>
+      <c r="A84" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>621</v>
       </c>
       <c r="D84" s="3">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>YS</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
+      <c r="A85" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>623</v>
       </c>
       <c r="D85" s="3">
         <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>SOL</t>
-        </is>
+      <c r="A86" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="D86" s="3">
         <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>STY</t>
-        </is>
+      <c r="A87" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="D87" s="3">
         <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>SKP</t>
-        </is>
+      <c r="A88" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="D88" s="3">
         <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>SND</t>
-        </is>
+      <c r="A89" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="D89" s="3">
         <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
+      <c r="A90" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>633</v>
       </c>
       <c r="D90" s="3">
         <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>TRF</t>
-        </is>
+      <c r="A91" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="D91" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>YW</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>WKF</t>
-        </is>
+      <c r="A92" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="D92" s="3">
         <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>WLL</t>
-        </is>
+      <c r="A93" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="D93" s="3">
         <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>WGN</t>
-        </is>
+      <c r="A94" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>641</v>
       </c>
       <c r="D94" s="3">
         <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>WRL</t>
-        </is>
+      <c r="A95" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="D95" s="3">
         <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>WLV</t>
-        </is>
+      <c r="A96" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>645</v>
       </c>
       <c r="D96" s="3">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>BAS</t>
-        </is>
+      <c r="A97" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>647</v>
       </c>
       <c r="D97" s="3">
         <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>BBD</t>
-        </is>
+      <c r="A98" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>649</v>
       </c>
       <c r="D98" s="3">
         <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>BDF</t>
-        </is>
+      <c r="A99" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>651</v>
       </c>
       <c r="D99" s="3">
         <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>BP</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>BPL</t>
-        </is>
+      <c r="A100" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>653</v>
       </c>
       <c r="D100" s="3">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>BMH</t>
-        </is>
+      <c r="A101" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>655</v>
       </c>
       <c r="D101" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>BF</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>BRC</t>
-        </is>
+      <c r="A102" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>657</v>
       </c>
       <c r="D102" s="3">
         <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>BH</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
+      <c r="A103" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>659</v>
       </c>
       <c r="D103" s="3">
         <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>BST</t>
-        </is>
+      <c r="A104" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>661</v>
       </c>
       <c r="D104" s="3">
         <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>CBF</t>
-        </is>
+      <c r="A105" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>663</v>
       </c>
       <c r="D105" s="3">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>CHE</t>
-        </is>
+      <c r="A106" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>665</v>
       </c>
       <c r="D106" s="3">
         <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>CHW</t>
-        </is>
+      <c r="A107" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>667</v>
       </c>
       <c r="D107" s="3">
         <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>CON</t>
-        </is>
+      <c r="A108" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>669</v>
       </c>
       <c r="D108" s="3">
         <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>DL</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
+      <c r="A109" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="D109" s="3">
         <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>DER</t>
-        </is>
+      <c r="A110" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>673</v>
       </c>
       <c r="D110" s="3">
         <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>DU</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>DUR</t>
-        </is>
+      <c r="A111" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>675</v>
       </c>
       <c r="D111" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>ER</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>ERY</t>
-        </is>
+      <c r="A112" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>677</v>
       </c>
       <c r="D112" s="3">
         <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
+      <c r="A113" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>679</v>
       </c>
       <c r="D113" s="3">
         <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>HPL</t>
-        </is>
+      <c r="A114" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>681</v>
       </c>
       <c r="D114" s="3">
         <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>HW</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>HEF</t>
-        </is>
+      <c r="A115" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="D115" s="3">
         <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>IW</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>IOW</t>
-        </is>
+      <c r="A116" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="D116" s="3">
         <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>KHL</t>
-        </is>
+      <c r="A117" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="D117" s="3">
         <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>LCE</t>
-        </is>
+      <c r="A118" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>689</v>
       </c>
       <c r="D118" s="3">
         <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>LUT</t>
-        </is>
+      <c r="A119" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>691</v>
       </c>
       <c r="D119" s="3">
         <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>MDB</t>
-        </is>
+      <c r="A120" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>695</v>
       </c>
       <c r="D120" s="3">
         <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>MIK</t>
-        </is>
+      <c r="A121" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>697</v>
       </c>
       <c r="D121" s="3">
         <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>NEL</t>
-        </is>
+      <c r="A122" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>699</v>
       </c>
       <c r="D122" s="3">
         <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>NLN</t>
-        </is>
+      <c r="A123" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>701</v>
       </c>
       <c r="D123" s="3">
         <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>NSM</t>
-        </is>
+      <c r="A124" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>703</v>
       </c>
       <c r="D124" s="3">
         <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>NBL</t>
-        </is>
+      <c r="A125" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>705</v>
       </c>
       <c r="D125" s="3">
         <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>NGM</t>
-        </is>
+      <c r="A126" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>707</v>
       </c>
       <c r="D126" s="3">
         <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>PTE</t>
-        </is>
+      <c r="A127" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>709</v>
       </c>
       <c r="D127" s="3">
         <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>PY</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>PLY</t>
-        </is>
+      <c r="A128" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>711</v>
       </c>
       <c r="D128" s="3">
         <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
+      <c r="A129" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>713</v>
       </c>
       <c r="D129" s="3">
         <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
+      <c r="A130" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>715</v>
       </c>
       <c r="D130" s="3">
         <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>RDG</t>
-        </is>
+      <c r="A131" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>717</v>
       </c>
       <c r="D131" s="3">
         <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>RCC</t>
-        </is>
+      <c r="A132" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>719</v>
       </c>
       <c r="D132" s="3">
         <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>RUT</t>
-        </is>
+      <c r="A133" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>721</v>
       </c>
       <c r="D133" s="3">
         <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>SHR</t>
-        </is>
+      <c r="A134" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>723</v>
       </c>
       <c r="D134" s="3">
         <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>SLG</t>
-        </is>
+      <c r="A135" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>725</v>
       </c>
       <c r="D135" s="3">
         <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>SGC</t>
-        </is>
+      <c r="A136" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>727</v>
       </c>
       <c r="D136" s="3">
         <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>STH</t>
-        </is>
+      <c r="A137" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>729</v>
       </c>
       <c r="D137" s="3">
         <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>SOS</t>
-        </is>
+      <c r="A138" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>731</v>
       </c>
       <c r="D138" s="3">
         <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
+      <c r="A139" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>733</v>
       </c>
       <c r="D139" s="3">
         <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>STE</t>
-        </is>
+      <c r="A140" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>735</v>
       </c>
       <c r="D140" s="3">
         <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>SWD</t>
-        </is>
+      <c r="A141" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>737</v>
       </c>
       <c r="D141" s="3">
         <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>TFW</t>
-        </is>
+      <c r="A142" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>739</v>
       </c>
       <c r="D142" s="3">
         <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>THR</t>
-        </is>
+      <c r="A143" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>741</v>
       </c>
       <c r="D143" s="3">
         <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>TOB</t>
-        </is>
+      <c r="A144" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>743</v>
       </c>
       <c r="D144" s="3">
         <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>WRT</t>
-        </is>
+      <c r="A145" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>745</v>
       </c>
       <c r="D145" s="3">
         <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>WBK</t>
-        </is>
+      <c r="A146" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>747</v>
       </c>
       <c r="D146" s="3">
         <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>WIL</t>
-        </is>
+      <c r="A147" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>749</v>
       </c>
       <c r="D147" s="3">
         <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>WNM</t>
-        </is>
+      <c r="A148" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>751</v>
       </c>
       <c r="D148" s="3">
         <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>WOK</t>
-        </is>
+      <c r="A149" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>753</v>
       </c>
       <c r="D149" s="3">
         <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>YK</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>YOR</t>
-        </is>
+      <c r="A150" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>755</v>
       </c>
       <c r="D150" s="3">
         <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>LND</t>
-        </is>
+      <c r="A151" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>757</v>
       </c>
       <c r="D151" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>ANT</t>
-        </is>
+      <c r="A152" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>759</v>
       </c>
       <c r="D152" s="3">
         <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>ARD</t>
-        </is>
+      <c r="A153" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>761</v>
       </c>
       <c r="D153" s="3">
         <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
+      <c r="A154" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>763</v>
       </c>
       <c r="D154" s="3">
         <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>BLA</t>
-        </is>
+      <c r="A155" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>765</v>
       </c>
       <c r="D155" s="3">
         <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>BY</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>BLY</t>
-        </is>
+      <c r="A156" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>767</v>
       </c>
       <c r="D156" s="3">
         <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>BN</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>BNB</t>
-        </is>
+      <c r="A157" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>769</v>
       </c>
       <c r="D157" s="3">
         <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>BFS</t>
-        </is>
+      <c r="A158" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>771</v>
       </c>
       <c r="D158" s="3">
         <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>CKF</t>
-        </is>
+      <c r="A159" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>773</v>
       </c>
       <c r="D159" s="3">
         <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>CSR</t>
-        </is>
+      <c r="A160" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>775</v>
       </c>
       <c r="D160" s="3">
         <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>CLR</t>
-        </is>
+      <c r="A161" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>777</v>
       </c>
       <c r="D161" s="3">
         <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>CKT</t>
-        </is>
+      <c r="A162" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>779</v>
       </c>
       <c r="D162" s="3">
         <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>CG</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>CGV</t>
-        </is>
+      <c r="A163" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>781</v>
       </c>
       <c r="D163" s="3">
         <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>LD</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>DRY</t>
-        </is>
+      <c r="A164" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>783</v>
       </c>
       <c r="D164" s="3">
         <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>DOW</t>
-        </is>
+      <c r="A165" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>785</v>
       </c>
       <c r="D165" s="3">
         <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>DGN</t>
-        </is>
+      <c r="A166" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>787</v>
       </c>
       <c r="D166" s="3">
         <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>FM</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>FER</t>
-        </is>
+      <c r="A167" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>789</v>
       </c>
       <c r="D167" s="3">
         <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>LRN</t>
-        </is>
+      <c r="A168" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>791</v>
       </c>
       <c r="D168" s="3">
         <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>LM</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>LMV</t>
-        </is>
+      <c r="A169" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>793</v>
       </c>
       <c r="D169" s="3">
         <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>LS</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>LSB</t>
-        </is>
+      <c r="A170" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>795</v>
       </c>
       <c r="D170" s="3">
         <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>MFT</t>
-        </is>
+      <c r="A171" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>797</v>
       </c>
       <c r="D171" s="3">
         <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>MYL</t>
-        </is>
+      <c r="A172" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>799</v>
       </c>
       <c r="D172" s="3">
         <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
+      <c r="A173" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>801</v>
       </c>
       <c r="D173" s="3">
         <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>NTA</t>
-        </is>
+      <c r="A174" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>803</v>
       </c>
       <c r="D174" s="3">
         <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>NDN</t>
-        </is>
+      <c r="A175" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>805</v>
       </c>
       <c r="D175" s="3">
         <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>OM</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>OMH</t>
-        </is>
+      <c r="A176" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>807</v>
       </c>
       <c r="D176" s="3">
         <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>SR</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>STB</t>
-        </is>
+      <c r="A177" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>809</v>
       </c>
       <c r="D177" s="3">
         <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>ABE</t>
-        </is>
+      <c r="A178" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>811</v>
       </c>
       <c r="D178" s="3">
         <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>ABD</t>
-        </is>
+      <c r="A179" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>813</v>
       </c>
       <c r="D179" s="3">
         <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>ANS</t>
-        </is>
+      <c r="A180" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>815</v>
       </c>
       <c r="D180" s="3">
         <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>AGB</t>
-        </is>
+      <c r="A181" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>817</v>
       </c>
       <c r="D181" s="3">
         <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>CLK</t>
-        </is>
+      <c r="A182" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>819</v>
       </c>
       <c r="D182" s="3">
         <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>DGY</t>
-        </is>
+      <c r="A183" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>821</v>
       </c>
       <c r="D183" s="3">
         <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>DND</t>
-        </is>
+      <c r="A184" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>823</v>
       </c>
       <c r="D184" s="3">
         <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>EAY</t>
-        </is>
+      <c r="A185" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>825</v>
       </c>
       <c r="D185" s="3">
         <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>EDU</t>
-        </is>
+      <c r="A186" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>827</v>
       </c>
       <c r="D186" s="3">
         <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>ELN</t>
-        </is>
+      <c r="A187" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>829</v>
       </c>
       <c r="D187" s="3">
         <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>ERW</t>
-        </is>
+      <c r="A188" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>831</v>
       </c>
       <c r="D188" s="3">
         <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>EDH</t>
-        </is>
+      <c r="A189" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>833</v>
       </c>
       <c r="D189" s="3">
         <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>WL</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>ELS</t>
-        </is>
+      <c r="A190" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="D190" s="3">
         <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>FAL</t>
-        </is>
+      <c r="A191" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>837</v>
       </c>
       <c r="D191" s="3">
         <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>FIF</t>
-        </is>
+      <c r="A192" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>839</v>
       </c>
       <c r="D192" s="3">
         <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>GLG</t>
-        </is>
+      <c r="A193" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>841</v>
       </c>
       <c r="D193" s="3">
         <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>HI</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>HLD</t>
-        </is>
+      <c r="A194" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>843</v>
       </c>
       <c r="D194" s="3">
         <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>IVC</t>
-        </is>
+      <c r="A195" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>845</v>
       </c>
       <c r="D195" s="3">
         <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>MLN</t>
-        </is>
+      <c r="A196" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>847</v>
       </c>
       <c r="D196" s="3">
         <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>MRY</t>
-        </is>
+      <c r="A197" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>849</v>
       </c>
       <c r="D197" s="3">
         <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>NAY</t>
-        </is>
+      <c r="A198" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>851</v>
       </c>
       <c r="D198" s="3">
         <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>NLK</t>
-        </is>
+      <c r="A199" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>853</v>
       </c>
       <c r="D199" s="3">
         <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>ORK</t>
-        </is>
+      <c r="A200" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>855</v>
       </c>
       <c r="D200" s="3">
         <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>PKN</t>
-        </is>
+      <c r="A201" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>857</v>
       </c>
       <c r="D201" s="3">
         <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>RFW</t>
-        </is>
+      <c r="A202" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>859</v>
       </c>
       <c r="D202" s="3">
         <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>SCB</t>
-        </is>
+      <c r="A203" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>861</v>
       </c>
       <c r="D203" s="3">
         <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>ZET</t>
-        </is>
+      <c r="A204" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>863</v>
       </c>
       <c r="D204" s="3">
         <v>203</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>SAY</t>
-        </is>
+      <c r="A205" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>865</v>
       </c>
       <c r="D205" s="3">
         <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>SLK</t>
-        </is>
+      <c r="A206" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>867</v>
       </c>
       <c r="D206" s="3">
         <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>STG</t>
-        </is>
+      <c r="A207" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>869</v>
       </c>
       <c r="D207" s="3">
         <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>WDU</t>
-        </is>
+      <c r="A208" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>871</v>
       </c>
       <c r="D208" s="3">
         <v>207</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>WLN</t>
-        </is>
+      <c r="A209" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>873</v>
       </c>
       <c r="D209" s="3">
         <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr">
-        <is>
-          <t>BGW</t>
-        </is>
+      <c r="A210" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>875</v>
       </c>
       <c r="D210" s="3">
         <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>BGE</t>
-        </is>
+      <c r="A211" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>877</v>
       </c>
       <c r="D211" s="3">
         <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>CRF</t>
-        </is>
+      <c r="A212" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>881</v>
       </c>
       <c r="D212" s="3">
         <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>DY</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>CMN</t>
-        </is>
+      <c r="A213" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>883</v>
       </c>
       <c r="D213" s="3">
         <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>DY</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>CGN</t>
-        </is>
+      <c r="A214" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>885</v>
       </c>
       <c r="D214" s="3">
         <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
+      <c r="A215" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>889</v>
       </c>
       <c r="D215" s="3">
         <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>FLN</t>
-        </is>
+      <c r="A216" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>891</v>
       </c>
       <c r="D216" s="3">
         <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>GY</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>GWN</t>
-        </is>
+      <c r="A217" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>893</v>
       </c>
       <c r="D217" s="3">
         <v>216</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>GY</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>AGY</t>
-        </is>
+      <c r="A218" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>895</v>
       </c>
       <c r="D218" s="3">
         <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>MTY</t>
-        </is>
+      <c r="A219" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>897</v>
       </c>
       <c r="D219" s="3">
         <v>218</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
+      <c r="A220" s="3" t="s">
+        <v>900</v>
       </c>
       <c r="B220" s="5"/>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>MDW</t>
-        </is>
+      <c r="C220" s="4" t="s">
+        <v>693</v>
       </c>
       <c r="D220" s="3">
         <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
+      <c r="A221" s="3" t="s">
+        <v>900</v>
       </c>
       <c r="B221" s="5"/>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>CAY</t>
-        </is>
+      <c r="C221" s="4" t="s">
+        <v>879</v>
       </c>
       <c r="D221" s="3">
         <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
+      <c r="A222" s="3" t="s">
+        <v>900</v>
       </c>
       <c r="B222" s="5"/>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>CWY</t>
-        </is>
+      <c r="C222" s="4" t="s">
+        <v>887</v>
       </c>
       <c r="D222" s="3">
         <v>221</v>
@@ -22211,7 +21355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC3BB94-C75C-C845-9B32-94401515EFD6}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22230,330 +21374,1603 @@
       <c r="C1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
+      <c r="A2" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>HH</t>
-        </is>
+      <c r="A3" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>987</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
+      <c r="A4" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>988</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
+      <c r="A5" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>989</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>NW</t>
-        </is>
+      <c r="A6" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>990</v>
       </c>
       <c r="D6" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>HE</t>
-        </is>
+      <c r="A7" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>991</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
+      <c r="A8" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>992</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>BW</t>
-        </is>
+      <c r="A9" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>993</v>
       </c>
       <c r="D9" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>BY</t>
-        </is>
+      <c r="A10" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>962</v>
       </c>
       <c r="D10" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
+      <c r="A11" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>979</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
+      <c r="A12" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>928</v>
       </c>
       <c r="D12" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
+      <c r="A13" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>927</v>
       </c>
       <c r="D13" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>MV</t>
-        </is>
+      <c r="A14" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>994</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
+      <c r="A15" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>950</v>
       </c>
       <c r="D15" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
+      <c r="A16" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>915</v>
       </c>
       <c r="D16" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
+      <c r="A17" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>953</v>
       </c>
       <c r="D17" s="3">
         <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CCE65A-1FFA-304A-A119-B02BA10B3749}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F90CCC3-E904-A247-9524-E51C14F69377}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D12" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D13" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D15" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D17" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D18" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D19" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D20" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D24" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D25" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D26" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D29" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D32" s="3">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="2" t="str">
+        <v>Country</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>SAP Value</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>EC Value</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>No.</v>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B2" s="4" t="str">
+        <v>01</v>
+      </c>
+      <c r="C2" s="4" t="str">
+        <v>VI</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <v>02</v>
+      </c>
+      <c r="C3" s="4" t="str">
+        <v>AB</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B4" s="4" t="str">
+        <v>03</v>
+      </c>
+      <c r="C4" s="4" t="str">
+        <v>A</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <v>04</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>AL</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <v>05</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>AV</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <v>06</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>BA</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <v>07</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <v>PM</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <v>08</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <v>BA1</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <v>09</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <v>BU</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <v>CC</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <v>CA</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <v>CS</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <v>13</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B15" s="4" t="str">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <v>CO</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B16" s="4" t="str">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <v>C</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B17" s="4" t="str">
+        <v>16</v>
+      </c>
+      <c r="C17" s="4" t="str">
+        <v>CU</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B18" s="4" t="str">
+        <v>17</v>
+      </c>
+      <c r="C18" s="4" t="str">
+        <v>GI</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B19" s="4" t="str">
+        <v>18</v>
+      </c>
+      <c r="C19" s="4" t="str">
+        <v>GR</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B20" s="4" t="str">
+        <v>19</v>
+      </c>
+      <c r="C20" s="4" t="str">
+        <v>GU</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B21" s="4" t="str">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4" t="str">
+        <v>SS</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B22" s="4" t="str">
+        <v>21</v>
+      </c>
+      <c r="C22" s="4" t="str">
+        <v>H</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B23" s="4" t="str">
+        <v>22</v>
+      </c>
+      <c r="C23" s="4" t="str">
+        <v>HU</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B24" s="4" t="str">
+        <v>23</v>
+      </c>
+      <c r="C24" s="4" t="str">
+        <v>J</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B25" s="4" t="str">
+        <v>24</v>
+      </c>
+      <c r="C25" s="4" t="str">
+        <v>LE</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B26" s="4" t="str">
+        <v>25</v>
+      </c>
+      <c r="C26" s="4" t="str">
+        <v>L</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B27" s="4" t="str">
+        <v>26</v>
+      </c>
+      <c r="C27" s="4" t="str">
+        <v>LO</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B28" s="4" t="str">
+        <v>27</v>
+      </c>
+      <c r="C28" s="4" t="str">
+        <v>LU</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B29" s="4" t="str">
+        <v>28</v>
+      </c>
+      <c r="C29" s="4" t="str">
+        <v>M</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B30" s="4" t="str">
+        <v>29</v>
+      </c>
+      <c r="C30" s="4" t="str">
+        <v>MA</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B31" s="4" t="str">
+        <v>30</v>
+      </c>
+      <c r="C31" s="4" t="str">
+        <v>MU</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B32" s="4" t="str">
+        <v>31</v>
+      </c>
+      <c r="C32" s="4" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B33" s="4" t="str">
+        <v>32</v>
+      </c>
+      <c r="C33" s="4" t="str">
+        <v>OR</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B34" s="4" t="str">
+        <v>33</v>
+      </c>
+      <c r="C34" s="4" t="str">
+        <v>O</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B35" s="4" t="str">
+        <v>34</v>
+      </c>
+      <c r="C35" s="4" t="str">
+        <v>P</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B36" s="4" t="str">
+        <v>35</v>
+      </c>
+      <c r="C36" s="4" t="str">
+        <v>GC</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B37" s="4" t="str">
+        <v>36</v>
+      </c>
+      <c r="C37" s="4" t="str">
+        <v>PO</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B38" s="4" t="str">
+        <v>37</v>
+      </c>
+      <c r="C38" s="4" t="str">
+        <v>SA</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B39" s="4" t="str">
+        <v>38</v>
+      </c>
+      <c r="C39" s="4" t="str">
+        <v>TF</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B40" s="4" t="str">
+        <v>39</v>
+      </c>
+      <c r="C40" s="4" t="str">
+        <v>S</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B41" s="4" t="str">
+        <v>40</v>
+      </c>
+      <c r="C41" s="4" t="str">
+        <v>SG</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B42" s="4" t="str">
+        <v>41</v>
+      </c>
+      <c r="C42" s="4" t="str">
+        <v>SE</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B43" s="4" t="str">
+        <v>42</v>
+      </c>
+      <c r="C43" s="4" t="str">
+        <v>SO</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B44" s="4" t="str">
+        <v>43</v>
+      </c>
+      <c r="C44" s="4" t="str">
+        <v>T</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B45" s="4" t="str">
+        <v>44</v>
+      </c>
+      <c r="C45" s="4" t="str">
+        <v>TE</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B46" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="C46" s="4" t="str">
+        <v>TO</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B47" s="4" t="str">
+        <v>46</v>
+      </c>
+      <c r="C47" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B48" s="4" t="str">
+        <v>47</v>
+      </c>
+      <c r="C48" s="4" t="str">
+        <v>VA</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B49" s="4" t="str">
+        <v>48</v>
+      </c>
+      <c r="C49" s="4" t="str">
+        <v>BI</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B50" s="4" t="str">
+        <v>49</v>
+      </c>
+      <c r="C50" s="4" t="str">
+        <v>ZA</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B51" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="C51" s="4" t="str">
+        <v>Z</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="4" t="str">
+        <v>CE</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="4" t="str">
+        <v>ML</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/doc/state_mapping.xlsx
+++ b/doc/state_mapping.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Austria T005S Map" sheetId="5" r:id="rId5"/>
     <sheet name="China T005S Map" sheetId="6" r:id="rId6"/>
     <sheet name="Spain T005S Map" sheetId="7" r:id="rId10"/>
+    <sheet name="Netherlands T005S Map" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -22976,4 +22977,177 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="2" t="str">
+        <v>Country</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>SAP Value</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>EC Value</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>No.</v>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4" t="str">
+        <v>DR</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4" t="str">
+        <v>FL</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="str">
+        <v>FR</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4" t="str">
+        <v>GE</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4" t="str">
+        <v>GR</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4" t="str">
+        <v>LI</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4" t="str">
+        <v>NB</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4" t="str">
+        <v>NH</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4" t="str">
+        <v>OV</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="4" t="str">
+        <v>ZH</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4" t="str">
+        <v>UT</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="3" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="4" t="str">
+        <v>ZE</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/state_mapping.xlsx
+++ b/doc/state_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wudaoyou/Dev/git/boc/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1C6279-1586-DF46-B347-B8B2B6A0A350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D2BF89-9CFF-9E4C-AD8E-EBF7C950F953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Germany T005S Map" sheetId="4" r:id="rId4"/>
     <sheet name="Austria T005S Map" sheetId="5" r:id="rId5"/>
     <sheet name="China T005S Map" sheetId="6" r:id="rId6"/>
-    <sheet name="Spain T005S Map" sheetId="7" r:id="rId10"/>
-    <sheet name="Netherlands T005S Map" sheetId="8" r:id="rId11"/>
+    <sheet name="Spain T005S Map" sheetId="7" r:id="rId7"/>
+    <sheet name="Netherlands T005S Map" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="1286">
   <si>
     <t>[OPERATOR]</t>
   </si>
@@ -3157,6 +3157,756 @@
   </si>
   <si>
     <t>300</t>
+  </si>
+  <si>
+    <t>Common Location Name</t>
+  </si>
+  <si>
+    <t>Schleswig-Holstein</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Lower Saxony</t>
+  </si>
+  <si>
+    <t>Bremen</t>
+  </si>
+  <si>
+    <t>North Rhine-Westphalia</t>
+  </si>
+  <si>
+    <t>Hesse</t>
+  </si>
+  <si>
+    <t>Rhineland-Palatinate</t>
+  </si>
+  <si>
+    <t>Baden-Württemberg</t>
+  </si>
+  <si>
+    <t>Bavaria</t>
+  </si>
+  <si>
+    <t>Saarland</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>Brandenburg</t>
+  </si>
+  <si>
+    <t>Mecklenburg-Vorpommern</t>
+  </si>
+  <si>
+    <t>Saxony</t>
+  </si>
+  <si>
+    <t>Saxony-Anhalt</t>
+  </si>
+  <si>
+    <t>Thuringia</t>
+  </si>
+  <si>
+    <t>Ain</t>
+  </si>
+  <si>
+    <t>Aisne</t>
+  </si>
+  <si>
+    <t>Allier</t>
+  </si>
+  <si>
+    <t>Alpes-de-Haute-Provence</t>
+  </si>
+  <si>
+    <t>Hautes-Alpes</t>
+  </si>
+  <si>
+    <t>Alpes-Maritimes</t>
+  </si>
+  <si>
+    <t>Ardèche</t>
+  </si>
+  <si>
+    <t>Ardennes</t>
+  </si>
+  <si>
+    <t>Ariège</t>
+  </si>
+  <si>
+    <t>Aube</t>
+  </si>
+  <si>
+    <t>Aude</t>
+  </si>
+  <si>
+    <t>Aveyron</t>
+  </si>
+  <si>
+    <t>Bouches-du-Rhône</t>
+  </si>
+  <si>
+    <t>Calvados</t>
+  </si>
+  <si>
+    <t>Cantal</t>
+  </si>
+  <si>
+    <t>Charente</t>
+  </si>
+  <si>
+    <t>Charente-Maritime</t>
+  </si>
+  <si>
+    <t>Cher</t>
+  </si>
+  <si>
+    <t>Corrèze</t>
+  </si>
+  <si>
+    <t>Corse-du-Sud</t>
+  </si>
+  <si>
+    <t>Haute-Corse</t>
+  </si>
+  <si>
+    <t>Côte-d'Or</t>
+  </si>
+  <si>
+    <t>Côtes-d'Armor</t>
+  </si>
+  <si>
+    <t>Creuse</t>
+  </si>
+  <si>
+    <t>Dordogne</t>
+  </si>
+  <si>
+    <t>Doubs</t>
+  </si>
+  <si>
+    <t>Drôme</t>
+  </si>
+  <si>
+    <t>Eure</t>
+  </si>
+  <si>
+    <t>Eure-et-Loir</t>
+  </si>
+  <si>
+    <t>Finistère</t>
+  </si>
+  <si>
+    <t>Gard</t>
+  </si>
+  <si>
+    <t>Haute-Garonne</t>
+  </si>
+  <si>
+    <t>Gers</t>
+  </si>
+  <si>
+    <t>Gironde</t>
+  </si>
+  <si>
+    <t>Hérault</t>
+  </si>
+  <si>
+    <t>Ille-et-Vilaine</t>
+  </si>
+  <si>
+    <t>Indre</t>
+  </si>
+  <si>
+    <t>Indre-et-Loire</t>
+  </si>
+  <si>
+    <t>Isère</t>
+  </si>
+  <si>
+    <t>Jura</t>
+  </si>
+  <si>
+    <t>Landes</t>
+  </si>
+  <si>
+    <t>Loir-et-Cher</t>
+  </si>
+  <si>
+    <t>Loire</t>
+  </si>
+  <si>
+    <t>Haute-Loire</t>
+  </si>
+  <si>
+    <t>Loire-Atlantique</t>
+  </si>
+  <si>
+    <t>Loiret</t>
+  </si>
+  <si>
+    <t>Lot</t>
+  </si>
+  <si>
+    <t>Lot-et-Garonne</t>
+  </si>
+  <si>
+    <t>Lozère</t>
+  </si>
+  <si>
+    <t>Maine-et-Loire</t>
+  </si>
+  <si>
+    <t>Manche</t>
+  </si>
+  <si>
+    <t>Marne</t>
+  </si>
+  <si>
+    <t>Haute-Marne</t>
+  </si>
+  <si>
+    <t>Mayenne</t>
+  </si>
+  <si>
+    <t>Moselle</t>
+  </si>
+  <si>
+    <t>Meuse</t>
+  </si>
+  <si>
+    <t>Morbihan</t>
+  </si>
+  <si>
+    <t>Meurthe-et-Moselle</t>
+  </si>
+  <si>
+    <t>Nièvre</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>Oise</t>
+  </si>
+  <si>
+    <t>Orne</t>
+  </si>
+  <si>
+    <t>Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>Puy-de-Dôme</t>
+  </si>
+  <si>
+    <t>Pyrénées-Atlantiques</t>
+  </si>
+  <si>
+    <t>Hautes-Pyrénées</t>
+  </si>
+  <si>
+    <t>Pyrénées-Orientales</t>
+  </si>
+  <si>
+    <t>Bas-Rhin</t>
+  </si>
+  <si>
+    <t>Haut-Rhin</t>
+  </si>
+  <si>
+    <t>Rhône</t>
+  </si>
+  <si>
+    <t>Haute-Saône</t>
+  </si>
+  <si>
+    <t>Saône-et-Loire</t>
+  </si>
+  <si>
+    <t>Sarthe</t>
+  </si>
+  <si>
+    <t>Savoie</t>
+  </si>
+  <si>
+    <t>Haute-Savoie</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Seine-Maritime</t>
+  </si>
+  <si>
+    <t>Seine-et-Marne</t>
+  </si>
+  <si>
+    <t>Yvelines</t>
+  </si>
+  <si>
+    <t>Deux-Sèvres</t>
+  </si>
+  <si>
+    <t>Somme</t>
+  </si>
+  <si>
+    <t>Tarn</t>
+  </si>
+  <si>
+    <t>Tarn-et-Garonne</t>
+  </si>
+  <si>
+    <t>Var</t>
+  </si>
+  <si>
+    <t>Vaucluse</t>
+  </si>
+  <si>
+    <t>Vendée</t>
+  </si>
+  <si>
+    <t>Vienne</t>
+  </si>
+  <si>
+    <t>Haute-Vienne</t>
+  </si>
+  <si>
+    <t>Vosges</t>
+  </si>
+  <si>
+    <t>Yonne</t>
+  </si>
+  <si>
+    <t>Territoire de Belfort</t>
+  </si>
+  <si>
+    <t>Essonne</t>
+  </si>
+  <si>
+    <t>Hauts-de-Seine</t>
+  </si>
+  <si>
+    <t>Seine-Saint-Denis</t>
+  </si>
+  <si>
+    <t>Val-de-Marne</t>
+  </si>
+  <si>
+    <t>Val-d'Oise</t>
+  </si>
+  <si>
+    <t>Guyane</t>
+  </si>
+  <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>Saint Pierre and Miquelon</t>
+  </si>
+  <si>
+    <t>Réunion</t>
+  </si>
+  <si>
+    <t>Wallis-et-Futuna</t>
+  </si>
+  <si>
+    <t>Saint Barthélemy</t>
+  </si>
+  <si>
+    <t>Clipperton Island</t>
+  </si>
+  <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
+    <t>New Caledonia</t>
+  </si>
+  <si>
+    <t>French Polynesia</t>
+  </si>
+  <si>
+    <t>French Southern Territories</t>
+  </si>
+  <si>
+    <t>Mayotte</t>
+  </si>
+  <si>
+    <t>St Helens</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>County Durham</t>
+  </si>
+  <si>
+    <t>City of London</t>
+  </si>
+  <si>
+    <t>City of Edinburgh</t>
+  </si>
+  <si>
+    <t>Scottish Borders</t>
+  </si>
+  <si>
+    <t>Burgenland</t>
+  </si>
+  <si>
+    <t>Carinthia</t>
+  </si>
+  <si>
+    <t>Lower Austria</t>
+  </si>
+  <si>
+    <t>Upper Austria</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Styria</t>
+  </si>
+  <si>
+    <t>Tyrol</t>
+  </si>
+  <si>
+    <t>Vorarlberg</t>
+  </si>
+  <si>
+    <t>Vienna</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>Tianjin</t>
+  </si>
+  <si>
+    <t>Anhui</t>
+  </si>
+  <si>
+    <t>Fujian</t>
+  </si>
+  <si>
+    <t>Gansu</t>
+  </si>
+  <si>
+    <t>Guangdong</t>
+  </si>
+  <si>
+    <t>Guizhou</t>
+  </si>
+  <si>
+    <t>Hainan</t>
+  </si>
+  <si>
+    <t>Hebei</t>
+  </si>
+  <si>
+    <t>Heilongjiang</t>
+  </si>
+  <si>
+    <t>Henan</t>
+  </si>
+  <si>
+    <t>Hubei</t>
+  </si>
+  <si>
+    <t>Hunan</t>
+  </si>
+  <si>
+    <t>Jiangsu</t>
+  </si>
+  <si>
+    <t>Jiangxi</t>
+  </si>
+  <si>
+    <t>Jilin</t>
+  </si>
+  <si>
+    <t>Liaoning</t>
+  </si>
+  <si>
+    <t>Qinghai</t>
+  </si>
+  <si>
+    <t>Shaanxi</t>
+  </si>
+  <si>
+    <t>Shandong</t>
+  </si>
+  <si>
+    <t>Shanxi</t>
+  </si>
+  <si>
+    <t>Sichuan</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>Yunnan</t>
+  </si>
+  <si>
+    <t>Zhejiang</t>
+  </si>
+  <si>
+    <t>Guangxi</t>
+  </si>
+  <si>
+    <t>Nei Mongol</t>
+  </si>
+  <si>
+    <t>Ningxia</t>
+  </si>
+  <si>
+    <t>Xinjiang</t>
+  </si>
+  <si>
+    <t>Xizang</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Álava</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Albacete</t>
+  </si>
+  <si>
+    <t>Alicante</t>
+  </si>
+  <si>
+    <t>Almería</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>Ávila</t>
+  </si>
+  <si>
+    <t>Badajoz</t>
+  </si>
+  <si>
+    <t>Balearic Islands</t>
+  </si>
+  <si>
+    <t>BA1</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Burgos</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Cáceres</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Castellón</t>
+  </si>
+  <si>
+    <t>Ciudad Real</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A Coruña</t>
+  </si>
+  <si>
+    <t>Cuenca</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Guadalajara</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Gipuzkoa</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Huelva</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>Huesca</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Jaén</t>
+  </si>
+  <si>
+    <t>León</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Lleida</t>
+  </si>
+  <si>
+    <t>La Rioja</t>
+  </si>
+  <si>
+    <t>Lugo</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>Málaga</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>Murcia</t>
+  </si>
+  <si>
+    <t>Navarra</t>
+  </si>
+  <si>
+    <t>Ourense</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Asturias</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Palencia</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>Las Palmas</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>Pontevedra</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>Salamanca</t>
+  </si>
+  <si>
+    <t>Santa Cruz de Tenerife</t>
+  </si>
+  <si>
+    <t>Cantabria</t>
+  </si>
+  <si>
+    <t>Segovia</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Soria</t>
+  </si>
+  <si>
+    <t>Tarragona</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>Teruel</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>Biscay</t>
+  </si>
+  <si>
+    <t>ZA</t>
+  </si>
+  <si>
+    <t>Zamora</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Melilla</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>99</t>
   </si>
 </sst>
 </file>
@@ -3354,6 +4104,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B72B8BE2-88D9-C475-E771-57A506196C41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA25D7B-CB28-3826-7E79-C1CD8CFF2ACE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16697,15 +17501,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3447E385-6E30-2F4A-8B4C-5328F4B9E411}">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -16718,8 +17523,11 @@
       <c r="D1" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>346</v>
       </c>
@@ -16732,8 +17540,11 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>346</v>
       </c>
@@ -16746,8 +17557,11 @@
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>346</v>
       </c>
@@ -16760,8 +17574,11 @@
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="4" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>346</v>
       </c>
@@ -16774,8 +17591,11 @@
       <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>346</v>
       </c>
@@ -16788,8 +17608,11 @@
       <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>346</v>
       </c>
@@ -16802,8 +17625,11 @@
       <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>346</v>
       </c>
@@ -16816,8 +17642,11 @@
       <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>346</v>
       </c>
@@ -16830,8 +17659,11 @@
       <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>346</v>
       </c>
@@ -16844,8 +17676,11 @@
       <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>346</v>
       </c>
@@ -16858,8 +17693,11 @@
       <c r="D11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>346</v>
       </c>
@@ -16872,8 +17710,11 @@
       <c r="D12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>346</v>
       </c>
@@ -16886,8 +17727,11 @@
       <c r="D13" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>346</v>
       </c>
@@ -16900,8 +17744,11 @@
       <c r="D14" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>346</v>
       </c>
@@ -16914,8 +17761,11 @@
       <c r="D15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>346</v>
       </c>
@@ -16928,8 +17778,11 @@
       <c r="D16" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>346</v>
       </c>
@@ -16942,8 +17795,11 @@
       <c r="D17" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="4" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>346</v>
       </c>
@@ -16956,8 +17812,11 @@
       <c r="D18" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="4" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>346</v>
       </c>
@@ -16970,8 +17829,11 @@
       <c r="D19" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="4" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>346</v>
       </c>
@@ -16984,8 +17846,11 @@
       <c r="D20" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="4" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>346</v>
       </c>
@@ -16998,8 +17863,11 @@
       <c r="D21" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="4" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>346</v>
       </c>
@@ -17012,8 +17880,11 @@
       <c r="D22" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="4" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>346</v>
       </c>
@@ -17026,8 +17897,11 @@
       <c r="D23" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="4" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>346</v>
       </c>
@@ -17040,8 +17914,11 @@
       <c r="D24" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="4" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>346</v>
       </c>
@@ -17054,8 +17931,11 @@
       <c r="D25" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="4" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>346</v>
       </c>
@@ -17068,8 +17948,11 @@
       <c r="D26" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="4" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>346</v>
       </c>
@@ -17082,8 +17965,11 @@
       <c r="D27" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="4" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>346</v>
       </c>
@@ -17096,8 +17982,11 @@
       <c r="D28" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="4" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>346</v>
       </c>
@@ -17110,8 +17999,11 @@
       <c r="D29" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E29" s="4" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>346</v>
       </c>
@@ -17124,8 +18016,11 @@
       <c r="D30" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="4" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>346</v>
       </c>
@@ -17138,8 +18033,11 @@
       <c r="D31" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="4" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>346</v>
       </c>
@@ -17152,8 +18050,11 @@
       <c r="D32" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="4" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>346</v>
       </c>
@@ -17166,8 +18067,11 @@
       <c r="D33" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E33" s="4" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>346</v>
       </c>
@@ -17180,8 +18084,11 @@
       <c r="D34" s="3">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="4" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>346</v>
       </c>
@@ -17194,8 +18101,11 @@
       <c r="D35" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="4" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>346</v>
       </c>
@@ -17208,8 +18118,11 @@
       <c r="D36" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="4" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>346</v>
       </c>
@@ -17222,8 +18135,11 @@
       <c r="D37" s="3">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="4" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>346</v>
       </c>
@@ -17236,8 +18152,11 @@
       <c r="D38" s="3">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="4" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>346</v>
       </c>
@@ -17250,8 +18169,11 @@
       <c r="D39" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="4" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>346</v>
       </c>
@@ -17264,8 +18186,11 @@
       <c r="D40" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="4" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>346</v>
       </c>
@@ -17278,8 +18203,11 @@
       <c r="D41" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="4" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>346</v>
       </c>
@@ -17292,8 +18220,11 @@
       <c r="D42" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="4" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>346</v>
       </c>
@@ -17306,8 +18237,11 @@
       <c r="D43" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="4" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>346</v>
       </c>
@@ -17320,8 +18254,11 @@
       <c r="D44" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="4" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>346</v>
       </c>
@@ -17334,8 +18271,11 @@
       <c r="D45" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="4" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>346</v>
       </c>
@@ -17348,8 +18288,11 @@
       <c r="D46" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="4" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>346</v>
       </c>
@@ -17362,8 +18305,11 @@
       <c r="D47" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="4" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>346</v>
       </c>
@@ -17376,8 +18322,11 @@
       <c r="D48" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E48" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>346</v>
       </c>
@@ -17390,8 +18339,11 @@
       <c r="D49" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="4" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>346</v>
       </c>
@@ -17404,8 +18356,11 @@
       <c r="D50" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="4" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>346</v>
       </c>
@@ -17418,8 +18373,11 @@
       <c r="D51" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>346</v>
       </c>
@@ -17432,8 +18390,11 @@
       <c r="D52" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="4" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>346</v>
       </c>
@@ -17446,8 +18407,11 @@
       <c r="D53" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="4" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -17460,8 +18424,11 @@
       <c r="D54" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="4" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>346</v>
       </c>
@@ -17474,8 +18441,11 @@
       <c r="D55" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="4" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>346</v>
       </c>
@@ -17488,8 +18458,11 @@
       <c r="D56" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E56" s="4" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>346</v>
       </c>
@@ -17502,8 +18475,11 @@
       <c r="D57" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E57" s="4" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>346</v>
       </c>
@@ -17516,8 +18492,11 @@
       <c r="D58" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E58" s="4" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>346</v>
       </c>
@@ -17530,8 +18509,11 @@
       <c r="D59" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="4" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>346</v>
       </c>
@@ -17544,8 +18526,11 @@
       <c r="D60" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E60" s="4" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>346</v>
       </c>
@@ -17558,8 +18543,11 @@
       <c r="D61" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E61" s="4" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>346</v>
       </c>
@@ -17572,8 +18560,11 @@
       <c r="D62" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E62" s="4" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>346</v>
       </c>
@@ -17586,8 +18577,11 @@
       <c r="D63" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E63" s="4" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>346</v>
       </c>
@@ -17600,8 +18594,11 @@
       <c r="D64" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E64" s="4" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>346</v>
       </c>
@@ -17614,8 +18611,11 @@
       <c r="D65" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E65" s="4" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>346</v>
       </c>
@@ -17628,8 +18628,11 @@
       <c r="D66" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E66" s="4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>346</v>
       </c>
@@ -17642,8 +18645,11 @@
       <c r="D67" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E67" s="4" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>346</v>
       </c>
@@ -17656,8 +18662,11 @@
       <c r="D68" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E68" s="4" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>346</v>
       </c>
@@ -17670,8 +18679,11 @@
       <c r="D69" s="3">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E69" s="4" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>346</v>
       </c>
@@ -17684,8 +18696,11 @@
       <c r="D70" s="3">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E70" s="4" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>346</v>
       </c>
@@ -17698,8 +18713,11 @@
       <c r="D71" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E71" s="4" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>346</v>
       </c>
@@ -17712,8 +18730,11 @@
       <c r="D72" s="3">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E72" s="4" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>346</v>
       </c>
@@ -17726,8 +18747,11 @@
       <c r="D73" s="3">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E73" s="4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>346</v>
       </c>
@@ -17740,8 +18764,11 @@
       <c r="D74" s="3">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E74" s="4" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>346</v>
       </c>
@@ -17754,8 +18781,11 @@
       <c r="D75" s="3">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E75" s="4" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>346</v>
       </c>
@@ -17768,8 +18798,11 @@
       <c r="D76" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E76" s="4" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>346</v>
       </c>
@@ -17782,8 +18815,11 @@
       <c r="D77" s="3">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E77" s="4" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>346</v>
       </c>
@@ -17796,8 +18832,11 @@
       <c r="D78" s="3">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E78" s="4" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>346</v>
       </c>
@@ -17810,8 +18849,11 @@
       <c r="D79" s="3">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E79" s="4" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>346</v>
       </c>
@@ -17824,8 +18866,11 @@
       <c r="D80" s="3">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E80" s="4" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>346</v>
       </c>
@@ -17838,8 +18883,11 @@
       <c r="D81" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E81" s="4" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>346</v>
       </c>
@@ -17852,8 +18900,11 @@
       <c r="D82" s="3">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E82" s="4" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>346</v>
       </c>
@@ -17866,8 +18917,11 @@
       <c r="D83" s="3">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E83" s="4" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>346</v>
       </c>
@@ -17880,8 +18934,11 @@
       <c r="D84" s="3">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E84" s="4" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>346</v>
       </c>
@@ -17894,8 +18951,11 @@
       <c r="D85" s="3">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E85" s="4" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>346</v>
       </c>
@@ -17908,8 +18968,11 @@
       <c r="D86" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E86" s="4" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>346</v>
       </c>
@@ -17922,8 +18985,11 @@
       <c r="D87" s="3">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E87" s="4" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>346</v>
       </c>
@@ -17936,8 +19002,11 @@
       <c r="D88" s="3">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E88" s="4" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>346</v>
       </c>
@@ -17950,8 +19019,11 @@
       <c r="D89" s="3">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E89" s="4" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>346</v>
       </c>
@@ -17964,8 +19036,11 @@
       <c r="D90" s="3">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E90" s="4" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>346</v>
       </c>
@@ -17978,8 +19053,11 @@
       <c r="D91" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E91" s="4" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>346</v>
       </c>
@@ -17992,8 +19070,11 @@
       <c r="D92" s="3">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E92" s="4" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>346</v>
       </c>
@@ -18006,8 +19087,11 @@
       <c r="D93" s="3">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E93" s="4" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>346</v>
       </c>
@@ -18020,8 +19104,11 @@
       <c r="D94" s="3">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E94" s="4" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>346</v>
       </c>
@@ -18034,8 +19121,11 @@
       <c r="D95" s="3">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E95" s="4" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>346</v>
       </c>
@@ -18048,8 +19138,11 @@
       <c r="D96" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E96" s="4" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>346</v>
       </c>
@@ -18062,8 +19155,11 @@
       <c r="D97" s="3">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E97" s="4" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>346</v>
       </c>
@@ -18076,8 +19172,11 @@
       <c r="D98" s="3">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E98" s="4" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>346</v>
       </c>
@@ -18090,8 +19189,11 @@
       <c r="D99" s="3">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E99" s="4" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>346</v>
       </c>
@@ -18104,8 +19206,11 @@
       <c r="D100" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E100" s="4" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>346</v>
       </c>
@@ -18118,8 +19223,11 @@
       <c r="D101" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E101" s="4" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>346</v>
       </c>
@@ -18132,8 +19240,11 @@
       <c r="D102" s="3">
         <v>101</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E102" s="4" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>346</v>
       </c>
@@ -18146,89 +19257,127 @@
       <c r="D103" s="3">
         <v>102</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E103" s="4" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B104" s="5"/>
+      <c r="B104" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C104" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D104" s="3">
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E104" s="4" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B105" s="5"/>
+      <c r="B105" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C105" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D105" s="3">
         <v>104</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E105" s="4" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B106" s="5"/>
+      <c r="B106" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C106" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D106" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E106" s="4" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B107" s="5"/>
+      <c r="B107" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C107" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D107" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E107" s="4" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B108" s="5"/>
+      <c r="B108" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C108" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D108" s="3">
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E108" s="4" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B109" s="5"/>
+      <c r="B109" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C109" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D109" s="3">
         <v>108</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E109" s="4" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B110" s="5"/>
+      <c r="B110" s="5" t="s">
+        <v>1285</v>
+      </c>
       <c r="C110" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D110" s="3">
         <v>109</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
@@ -18240,15 +19389,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D92772C-FCC0-9F4F-B254-1C7078C6A5A1}">
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -18261,8 +19411,11 @@
       <c r="D1" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>900</v>
       </c>
@@ -18275,8 +19428,11 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>900</v>
       </c>
@@ -18289,8 +19445,11 @@
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>900</v>
       </c>
@@ -18303,8 +19462,11 @@
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>900</v>
       </c>
@@ -18317,8 +19479,11 @@
       <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>900</v>
       </c>
@@ -18331,8 +19496,11 @@
       <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>900</v>
       </c>
@@ -18345,8 +19513,11 @@
       <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>900</v>
       </c>
@@ -18359,8 +19530,11 @@
       <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>900</v>
       </c>
@@ -18373,8 +19547,11 @@
       <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>900</v>
       </c>
@@ -18387,8 +19564,11 @@
       <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>900</v>
       </c>
@@ -18401,8 +19581,11 @@
       <c r="D11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>900</v>
       </c>
@@ -18415,8 +19598,11 @@
       <c r="D12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>900</v>
       </c>
@@ -18429,8 +19615,11 @@
       <c r="D13" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>900</v>
       </c>
@@ -18443,8 +19632,11 @@
       <c r="D14" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>900</v>
       </c>
@@ -18457,8 +19649,11 @@
       <c r="D15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>900</v>
       </c>
@@ -18471,8 +19666,11 @@
       <c r="D16" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>900</v>
       </c>
@@ -18485,8 +19683,11 @@
       <c r="D17" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>900</v>
       </c>
@@ -18499,8 +19700,11 @@
       <c r="D18" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>900</v>
       </c>
@@ -18513,8 +19717,11 @@
       <c r="D19" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>900</v>
       </c>
@@ -18527,8 +19734,11 @@
       <c r="D20" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>900</v>
       </c>
@@ -18541,8 +19751,11 @@
       <c r="D21" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>900</v>
       </c>
@@ -18555,8 +19768,11 @@
       <c r="D22" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>900</v>
       </c>
@@ -18569,8 +19785,11 @@
       <c r="D23" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>900</v>
       </c>
@@ -18583,8 +19802,11 @@
       <c r="D24" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>900</v>
       </c>
@@ -18597,8 +19819,11 @@
       <c r="D25" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>900</v>
       </c>
@@ -18611,8 +19836,11 @@
       <c r="D26" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>900</v>
       </c>
@@ -18625,8 +19853,11 @@
       <c r="D27" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>900</v>
       </c>
@@ -18639,8 +19870,11 @@
       <c r="D28" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>900</v>
       </c>
@@ -18653,8 +19887,11 @@
       <c r="D29" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E29" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>900</v>
       </c>
@@ -18667,8 +19904,11 @@
       <c r="D30" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>900</v>
       </c>
@@ -18681,8 +19921,11 @@
       <c r="D31" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="4" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>900</v>
       </c>
@@ -18695,8 +19938,11 @@
       <c r="D32" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>900</v>
       </c>
@@ -18709,8 +19955,11 @@
       <c r="D33" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E33" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>900</v>
       </c>
@@ -18723,8 +19972,11 @@
       <c r="D34" s="3">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>900</v>
       </c>
@@ -18737,8 +19989,11 @@
       <c r="D35" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>900</v>
       </c>
@@ -18751,8 +20006,11 @@
       <c r="D36" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>900</v>
       </c>
@@ -18765,8 +20023,11 @@
       <c r="D37" s="3">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>900</v>
       </c>
@@ -18779,8 +20040,11 @@
       <c r="D38" s="3">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>900</v>
       </c>
@@ -18793,8 +20057,11 @@
       <c r="D39" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>900</v>
       </c>
@@ -18807,8 +20074,11 @@
       <c r="D40" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>900</v>
       </c>
@@ -18821,8 +20091,11 @@
       <c r="D41" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>900</v>
       </c>
@@ -18835,8 +20108,11 @@
       <c r="D42" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>900</v>
       </c>
@@ -18849,8 +20125,11 @@
       <c r="D43" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>900</v>
       </c>
@@ -18863,8 +20142,11 @@
       <c r="D44" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>900</v>
       </c>
@@ -18877,8 +20159,11 @@
       <c r="D45" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>900</v>
       </c>
@@ -18891,8 +20176,11 @@
       <c r="D46" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>900</v>
       </c>
@@ -18905,8 +20193,11 @@
       <c r="D47" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>900</v>
       </c>
@@ -18919,8 +20210,11 @@
       <c r="D48" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E48" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>900</v>
       </c>
@@ -18933,8 +20227,11 @@
       <c r="D49" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>900</v>
       </c>
@@ -18947,8 +20244,11 @@
       <c r="D50" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>900</v>
       </c>
@@ -18961,8 +20261,11 @@
       <c r="D51" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>900</v>
       </c>
@@ -18975,8 +20278,11 @@
       <c r="D52" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>900</v>
       </c>
@@ -18989,8 +20295,11 @@
       <c r="D53" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>900</v>
       </c>
@@ -19003,8 +20312,11 @@
       <c r="D54" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>900</v>
       </c>
@@ -19017,8 +20329,11 @@
       <c r="D55" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>900</v>
       </c>
@@ -19031,8 +20346,11 @@
       <c r="D56" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E56" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>900</v>
       </c>
@@ -19045,8 +20363,11 @@
       <c r="D57" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E57" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>900</v>
       </c>
@@ -19059,8 +20380,11 @@
       <c r="D58" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E58" s="4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>900</v>
       </c>
@@ -19073,8 +20397,11 @@
       <c r="D59" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="4" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>900</v>
       </c>
@@ -19087,8 +20414,11 @@
       <c r="D60" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E60" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>900</v>
       </c>
@@ -19101,8 +20431,11 @@
       <c r="D61" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E61" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>900</v>
       </c>
@@ -19115,8 +20448,11 @@
       <c r="D62" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E62" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>900</v>
       </c>
@@ -19129,8 +20465,11 @@
       <c r="D63" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E63" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>900</v>
       </c>
@@ -19143,8 +20482,11 @@
       <c r="D64" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E64" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>900</v>
       </c>
@@ -19157,8 +20499,11 @@
       <c r="D65" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E65" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>900</v>
       </c>
@@ -19171,8 +20516,11 @@
       <c r="D66" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E66" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>900</v>
       </c>
@@ -19185,8 +20533,11 @@
       <c r="D67" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E67" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>900</v>
       </c>
@@ -19199,8 +20550,11 @@
       <c r="D68" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E68" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>900</v>
       </c>
@@ -19213,8 +20567,11 @@
       <c r="D69" s="3">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E69" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>900</v>
       </c>
@@ -19227,8 +20584,11 @@
       <c r="D70" s="3">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E70" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>900</v>
       </c>
@@ -19241,8 +20601,11 @@
       <c r="D71" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E71" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>900</v>
       </c>
@@ -19255,8 +20618,11 @@
       <c r="D72" s="3">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E72" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>900</v>
       </c>
@@ -19269,8 +20635,11 @@
       <c r="D73" s="3">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E73" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>900</v>
       </c>
@@ -19283,8 +20652,11 @@
       <c r="D74" s="3">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E74" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>900</v>
       </c>
@@ -19297,8 +20669,11 @@
       <c r="D75" s="3">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E75" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>900</v>
       </c>
@@ -19311,8 +20686,11 @@
       <c r="D76" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E76" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>900</v>
       </c>
@@ -19325,8 +20703,11 @@
       <c r="D77" s="3">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E77" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>900</v>
       </c>
@@ -19339,8 +20720,11 @@
       <c r="D78" s="3">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E78" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>900</v>
       </c>
@@ -19353,8 +20737,11 @@
       <c r="D79" s="3">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E79" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>900</v>
       </c>
@@ -19367,8 +20754,11 @@
       <c r="D80" s="3">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E80" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>900</v>
       </c>
@@ -19381,8 +20771,11 @@
       <c r="D81" s="3">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E81" s="4" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>900</v>
       </c>
@@ -19395,8 +20788,11 @@
       <c r="D82" s="3">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E82" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>900</v>
       </c>
@@ -19409,8 +20805,11 @@
       <c r="D83" s="3">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E83" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>900</v>
       </c>
@@ -19423,8 +20822,11 @@
       <c r="D84" s="3">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E84" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>900</v>
       </c>
@@ -19437,8 +20839,11 @@
       <c r="D85" s="3">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E85" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>900</v>
       </c>
@@ -19451,8 +20856,11 @@
       <c r="D86" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E86" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>900</v>
       </c>
@@ -19465,8 +20873,11 @@
       <c r="D87" s="3">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E87" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>900</v>
       </c>
@@ -19479,8 +20890,11 @@
       <c r="D88" s="3">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E88" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>900</v>
       </c>
@@ -19493,8 +20907,11 @@
       <c r="D89" s="3">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E89" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>900</v>
       </c>
@@ -19507,8 +20924,11 @@
       <c r="D90" s="3">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E90" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>900</v>
       </c>
@@ -19521,8 +20941,11 @@
       <c r="D91" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E91" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>900</v>
       </c>
@@ -19535,8 +20958,11 @@
       <c r="D92" s="3">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E92" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>900</v>
       </c>
@@ -19549,8 +20975,11 @@
       <c r="D93" s="3">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E93" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>900</v>
       </c>
@@ -19563,8 +20992,11 @@
       <c r="D94" s="3">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E94" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>900</v>
       </c>
@@ -19577,8 +21009,11 @@
       <c r="D95" s="3">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E95" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>900</v>
       </c>
@@ -19591,8 +21026,11 @@
       <c r="D96" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E96" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>900</v>
       </c>
@@ -19605,8 +21043,11 @@
       <c r="D97" s="3">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E97" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>900</v>
       </c>
@@ -19619,8 +21060,11 @@
       <c r="D98" s="3">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E98" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>900</v>
       </c>
@@ -19633,8 +21077,11 @@
       <c r="D99" s="3">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E99" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>900</v>
       </c>
@@ -19647,8 +21094,11 @@
       <c r="D100" s="3">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E100" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>900</v>
       </c>
@@ -19661,8 +21111,11 @@
       <c r="D101" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E101" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>900</v>
       </c>
@@ -19675,8 +21128,11 @@
       <c r="D102" s="3">
         <v>101</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E102" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>900</v>
       </c>
@@ -19689,8 +21145,11 @@
       <c r="D103" s="3">
         <v>102</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E103" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>900</v>
       </c>
@@ -19703,8 +21162,11 @@
       <c r="D104" s="3">
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E104" s="4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>900</v>
       </c>
@@ -19717,8 +21179,11 @@
       <c r="D105" s="3">
         <v>104</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E105" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>900</v>
       </c>
@@ -19731,8 +21196,11 @@
       <c r="D106" s="3">
         <v>105</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E106" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>900</v>
       </c>
@@ -19745,8 +21213,11 @@
       <c r="D107" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E107" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>900</v>
       </c>
@@ -19759,8 +21230,11 @@
       <c r="D108" s="3">
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E108" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>900</v>
       </c>
@@ -19773,8 +21247,11 @@
       <c r="D109" s="3">
         <v>108</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E109" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>900</v>
       </c>
@@ -19787,8 +21264,11 @@
       <c r="D110" s="3">
         <v>109</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E110" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>900</v>
       </c>
@@ -19801,8 +21281,11 @@
       <c r="D111" s="3">
         <v>110</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E111" s="4" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>900</v>
       </c>
@@ -19815,8 +21298,11 @@
       <c r="D112" s="3">
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E112" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>900</v>
       </c>
@@ -19829,8 +21315,11 @@
       <c r="D113" s="3">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E113" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>900</v>
       </c>
@@ -19843,8 +21332,11 @@
       <c r="D114" s="3">
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E114" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>900</v>
       </c>
@@ -19857,8 +21349,11 @@
       <c r="D115" s="3">
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E115" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>900</v>
       </c>
@@ -19871,8 +21366,11 @@
       <c r="D116" s="3">
         <v>115</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E116" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>900</v>
       </c>
@@ -19885,8 +21383,11 @@
       <c r="D117" s="3">
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E117" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>900</v>
       </c>
@@ -19899,8 +21400,11 @@
       <c r="D118" s="3">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E118" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>900</v>
       </c>
@@ -19913,8 +21417,11 @@
       <c r="D119" s="3">
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E119" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>900</v>
       </c>
@@ -19927,8 +21434,11 @@
       <c r="D120" s="3">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E120" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>900</v>
       </c>
@@ -19941,8 +21451,11 @@
       <c r="D121" s="3">
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E121" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>900</v>
       </c>
@@ -19955,8 +21468,11 @@
       <c r="D122" s="3">
         <v>121</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E122" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>900</v>
       </c>
@@ -19969,8 +21485,11 @@
       <c r="D123" s="3">
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E123" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>900</v>
       </c>
@@ -19983,8 +21502,11 @@
       <c r="D124" s="3">
         <v>123</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E124" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>900</v>
       </c>
@@ -19997,8 +21519,11 @@
       <c r="D125" s="3">
         <v>124</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E125" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>900</v>
       </c>
@@ -20011,8 +21536,11 @@
       <c r="D126" s="3">
         <v>125</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E126" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>900</v>
       </c>
@@ -20025,8 +21553,11 @@
       <c r="D127" s="3">
         <v>126</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E127" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>900</v>
       </c>
@@ -20039,8 +21570,11 @@
       <c r="D128" s="3">
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E128" s="4" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>900</v>
       </c>
@@ -20053,8 +21587,11 @@
       <c r="D129" s="3">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E129" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>900</v>
       </c>
@@ -20067,8 +21604,11 @@
       <c r="D130" s="3">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E130" s="4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>900</v>
       </c>
@@ -20081,8 +21621,11 @@
       <c r="D131" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E131" s="4" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>900</v>
       </c>
@@ -20095,8 +21638,11 @@
       <c r="D132" s="3">
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E132" s="4" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>900</v>
       </c>
@@ -20109,8 +21655,11 @@
       <c r="D133" s="3">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E133" s="4" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>900</v>
       </c>
@@ -20123,8 +21672,11 @@
       <c r="D134" s="3">
         <v>133</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E134" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>900</v>
       </c>
@@ -20137,8 +21689,11 @@
       <c r="D135" s="3">
         <v>134</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E135" s="4" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>900</v>
       </c>
@@ -20151,8 +21706,11 @@
       <c r="D136" s="3">
         <v>135</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E136" s="4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>900</v>
       </c>
@@ -20165,8 +21723,11 @@
       <c r="D137" s="3">
         <v>136</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E137" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>900</v>
       </c>
@@ -20179,8 +21740,11 @@
       <c r="D138" s="3">
         <v>137</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E138" s="4" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>900</v>
       </c>
@@ -20193,8 +21757,11 @@
       <c r="D139" s="3">
         <v>138</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E139" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>900</v>
       </c>
@@ -20207,8 +21774,11 @@
       <c r="D140" s="3">
         <v>139</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E140" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>900</v>
       </c>
@@ -20221,8 +21791,11 @@
       <c r="D141" s="3">
         <v>140</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E141" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>900</v>
       </c>
@@ -20235,8 +21808,11 @@
       <c r="D142" s="3">
         <v>141</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E142" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>900</v>
       </c>
@@ -20249,8 +21825,11 @@
       <c r="D143" s="3">
         <v>142</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E143" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>900</v>
       </c>
@@ -20263,8 +21842,11 @@
       <c r="D144" s="3">
         <v>143</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E144" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>900</v>
       </c>
@@ -20277,8 +21859,11 @@
       <c r="D145" s="3">
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E145" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>900</v>
       </c>
@@ -20291,8 +21876,11 @@
       <c r="D146" s="3">
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E146" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>900</v>
       </c>
@@ -20305,8 +21893,11 @@
       <c r="D147" s="3">
         <v>146</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E147" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>900</v>
       </c>
@@ -20319,8 +21910,11 @@
       <c r="D148" s="3">
         <v>147</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E148" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>900</v>
       </c>
@@ -20333,8 +21927,11 @@
       <c r="D149" s="3">
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E149" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>900</v>
       </c>
@@ -20347,8 +21944,11 @@
       <c r="D150" s="3">
         <v>149</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E150" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>900</v>
       </c>
@@ -20361,8 +21961,11 @@
       <c r="D151" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E151" s="4" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>900</v>
       </c>
@@ -20375,8 +21978,11 @@
       <c r="D152" s="3">
         <v>151</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E152" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>900</v>
       </c>
@@ -20389,8 +21995,11 @@
       <c r="D153" s="3">
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E153" s="4" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>900</v>
       </c>
@@ -20403,8 +22012,11 @@
       <c r="D154" s="3">
         <v>153</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E154" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>900</v>
       </c>
@@ -20417,8 +22029,11 @@
       <c r="D155" s="3">
         <v>154</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E155" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>900</v>
       </c>
@@ -20431,8 +22046,11 @@
       <c r="D156" s="3">
         <v>155</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E156" s="4" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>900</v>
       </c>
@@ -20445,8 +22063,11 @@
       <c r="D157" s="3">
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E157" s="4" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>900</v>
       </c>
@@ -20459,8 +22080,11 @@
       <c r="D158" s="3">
         <v>157</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E158" s="4" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>900</v>
       </c>
@@ -20473,8 +22097,11 @@
       <c r="D159" s="3">
         <v>158</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E159" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>900</v>
       </c>
@@ -20487,8 +22114,11 @@
       <c r="D160" s="3">
         <v>159</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E160" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>900</v>
       </c>
@@ -20501,8 +22131,11 @@
       <c r="D161" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E161" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>900</v>
       </c>
@@ -20515,8 +22148,11 @@
       <c r="D162" s="3">
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E162" s="4" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>900</v>
       </c>
@@ -20529,8 +22165,11 @@
       <c r="D163" s="3">
         <v>162</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E163" s="4" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>900</v>
       </c>
@@ -20543,8 +22182,11 @@
       <c r="D164" s="3">
         <v>163</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E164" s="4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
         <v>900</v>
       </c>
@@ -20557,8 +22199,11 @@
       <c r="D165" s="3">
         <v>164</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E165" s="4" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>900</v>
       </c>
@@ -20571,8 +22216,11 @@
       <c r="D166" s="3">
         <v>165</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E166" s="4" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>900</v>
       </c>
@@ -20585,8 +22233,11 @@
       <c r="D167" s="3">
         <v>166</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E167" s="4" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>900</v>
       </c>
@@ -20599,8 +22250,11 @@
       <c r="D168" s="3">
         <v>167</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E168" s="4" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>900</v>
       </c>
@@ -20613,8 +22267,11 @@
       <c r="D169" s="3">
         <v>168</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E169" s="4" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>900</v>
       </c>
@@ -20627,8 +22284,11 @@
       <c r="D170" s="3">
         <v>169</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E170" s="4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>900</v>
       </c>
@@ -20641,8 +22301,11 @@
       <c r="D171" s="3">
         <v>170</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E171" s="4" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>900</v>
       </c>
@@ -20655,8 +22318,11 @@
       <c r="D172" s="3">
         <v>171</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E172" s="4" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>900</v>
       </c>
@@ -20669,8 +22335,11 @@
       <c r="D173" s="3">
         <v>172</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E173" s="4" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>900</v>
       </c>
@@ -20683,8 +22352,11 @@
       <c r="D174" s="3">
         <v>173</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E174" s="4" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>900</v>
       </c>
@@ -20697,8 +22369,11 @@
       <c r="D175" s="3">
         <v>174</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E175" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>900</v>
       </c>
@@ -20711,8 +22386,11 @@
       <c r="D176" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E176" s="4" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>900</v>
       </c>
@@ -20725,8 +22403,11 @@
       <c r="D177" s="3">
         <v>176</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E177" s="4" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>900</v>
       </c>
@@ -20739,8 +22420,11 @@
       <c r="D178" s="3">
         <v>177</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E178" s="4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>900</v>
       </c>
@@ -20753,8 +22437,11 @@
       <c r="D179" s="3">
         <v>178</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E179" s="4" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>900</v>
       </c>
@@ -20767,8 +22454,11 @@
       <c r="D180" s="3">
         <v>179</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E180" s="4" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>900</v>
       </c>
@@ -20781,8 +22471,11 @@
       <c r="D181" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E181" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>900</v>
       </c>
@@ -20795,8 +22488,11 @@
       <c r="D182" s="3">
         <v>181</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E182" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>900</v>
       </c>
@@ -20809,8 +22505,11 @@
       <c r="D183" s="3">
         <v>182</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E183" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>900</v>
       </c>
@@ -20823,8 +22522,11 @@
       <c r="D184" s="3">
         <v>183</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E184" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>900</v>
       </c>
@@ -20837,8 +22539,11 @@
       <c r="D185" s="3">
         <v>184</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E185" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>900</v>
       </c>
@@ -20851,8 +22556,11 @@
       <c r="D186" s="3">
         <v>185</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E186" s="4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>900</v>
       </c>
@@ -20865,8 +22573,11 @@
       <c r="D187" s="3">
         <v>186</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E187" s="4" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>900</v>
       </c>
@@ -20879,8 +22590,11 @@
       <c r="D188" s="3">
         <v>187</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E188" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>900</v>
       </c>
@@ -20893,8 +22607,11 @@
       <c r="D189" s="3">
         <v>188</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E189" s="4" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
         <v>900</v>
       </c>
@@ -20907,8 +22624,11 @@
       <c r="D190" s="3">
         <v>189</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E190" s="4" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>900</v>
       </c>
@@ -20921,8 +22641,11 @@
       <c r="D191" s="3">
         <v>190</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E191" s="4" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>900</v>
       </c>
@@ -20935,8 +22658,11 @@
       <c r="D192" s="3">
         <v>191</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E192" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>900</v>
       </c>
@@ -20949,8 +22675,11 @@
       <c r="D193" s="3">
         <v>192</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E193" s="4" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>900</v>
       </c>
@@ -20963,8 +22692,11 @@
       <c r="D194" s="3">
         <v>193</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E194" s="4" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>900</v>
       </c>
@@ -20977,8 +22709,11 @@
       <c r="D195" s="3">
         <v>194</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E195" s="4" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>900</v>
       </c>
@@ -20991,8 +22726,11 @@
       <c r="D196" s="3">
         <v>195</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E196" s="4" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>900</v>
       </c>
@@ -21005,8 +22743,11 @@
       <c r="D197" s="3">
         <v>196</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E197" s="4" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
         <v>900</v>
       </c>
@@ -21019,8 +22760,11 @@
       <c r="D198" s="3">
         <v>197</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E198" s="4" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>900</v>
       </c>
@@ -21033,8 +22777,11 @@
       <c r="D199" s="3">
         <v>198</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E199" s="4" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>900</v>
       </c>
@@ -21047,8 +22794,11 @@
       <c r="D200" s="3">
         <v>199</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E200" s="4" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>900</v>
       </c>
@@ -21061,8 +22811,11 @@
       <c r="D201" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E201" s="4" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>900</v>
       </c>
@@ -21075,8 +22828,11 @@
       <c r="D202" s="3">
         <v>201</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E202" s="4" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>900</v>
       </c>
@@ -21089,8 +22845,11 @@
       <c r="D203" s="3">
         <v>202</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E203" s="4" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>900</v>
       </c>
@@ -21103,8 +22862,11 @@
       <c r="D204" s="3">
         <v>203</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E204" s="4" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>900</v>
       </c>
@@ -21117,8 +22879,11 @@
       <c r="D205" s="3">
         <v>204</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E205" s="4" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>900</v>
       </c>
@@ -21131,8 +22896,11 @@
       <c r="D206" s="3">
         <v>205</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E206" s="4" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>900</v>
       </c>
@@ -21145,8 +22913,11 @@
       <c r="D207" s="3">
         <v>206</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E207" s="4" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>900</v>
       </c>
@@ -21159,8 +22930,11 @@
       <c r="D208" s="3">
         <v>207</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E208" s="4" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>900</v>
       </c>
@@ -21173,8 +22947,11 @@
       <c r="D209" s="3">
         <v>208</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E209" s="4" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>900</v>
       </c>
@@ -21187,8 +22964,11 @@
       <c r="D210" s="3">
         <v>209</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E210" s="4" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>900</v>
       </c>
@@ -21201,8 +22981,11 @@
       <c r="D211" s="3">
         <v>210</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E211" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>900</v>
       </c>
@@ -21215,8 +22998,11 @@
       <c r="D212" s="3">
         <v>211</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E212" s="4" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>900</v>
       </c>
@@ -21229,8 +23015,11 @@
       <c r="D213" s="3">
         <v>212</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E213" s="4" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>900</v>
       </c>
@@ -21243,8 +23032,11 @@
       <c r="D214" s="3">
         <v>213</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E214" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>900</v>
       </c>
@@ -21257,8 +23049,11 @@
       <c r="D215" s="3">
         <v>214</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E215" s="4" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>900</v>
       </c>
@@ -21271,8 +23066,11 @@
       <c r="D216" s="3">
         <v>215</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E216" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>900</v>
       </c>
@@ -21285,8 +23083,11 @@
       <c r="D217" s="3">
         <v>216</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E217" s="4" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>900</v>
       </c>
@@ -21299,8 +23100,11 @@
       <c r="D218" s="3">
         <v>217</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E218" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>900</v>
       </c>
@@ -21313,8 +23117,11 @@
       <c r="D219" s="3">
         <v>218</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E219" s="4" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
         <v>900</v>
       </c>
@@ -21325,8 +23132,11 @@
       <c r="D220" s="3">
         <v>219</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E220" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>900</v>
       </c>
@@ -21337,8 +23147,11 @@
       <c r="D221" s="3">
         <v>220</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E221" s="4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>900</v>
       </c>
@@ -21348,6 +23161,9 @@
       </c>
       <c r="D222" s="3">
         <v>221</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -21357,15 +23173,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC3BB94-C75C-C845-9B32-94401515EFD6}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -21378,8 +23195,11 @@
       <c r="D1" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>986</v>
       </c>
@@ -21392,8 +23212,11 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>986</v>
       </c>
@@ -21406,8 +23229,11 @@
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>986</v>
       </c>
@@ -21420,8 +23246,11 @@
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="4" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>986</v>
       </c>
@@ -21434,8 +23263,11 @@
       <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>986</v>
       </c>
@@ -21448,8 +23280,11 @@
       <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>986</v>
       </c>
@@ -21462,8 +23297,11 @@
       <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>986</v>
       </c>
@@ -21476,8 +23314,11 @@
       <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>986</v>
       </c>
@@ -21490,8 +23331,11 @@
       <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>986</v>
       </c>
@@ -21504,8 +23348,11 @@
       <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>986</v>
       </c>
@@ -21518,8 +23365,11 @@
       <c r="D11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>986</v>
       </c>
@@ -21532,8 +23382,11 @@
       <c r="D12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>986</v>
       </c>
@@ -21546,8 +23399,11 @@
       <c r="D13" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>986</v>
       </c>
@@ -21560,8 +23416,11 @@
       <c r="D14" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>986</v>
       </c>
@@ -21574,8 +23433,11 @@
       <c r="D15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>986</v>
       </c>
@@ -21588,8 +23450,11 @@
       <c r="D16" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>986</v>
       </c>
@@ -21601,6 +23466,9 @@
       </c>
       <c r="D17" s="3">
         <v>16</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -21610,15 +23478,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CCE65A-1FFA-304A-A119-B02BA10B3749}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -21631,8 +23500,11 @@
       <c r="D1" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>995</v>
       </c>
@@ -21645,8 +23517,11 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>995</v>
       </c>
@@ -21659,8 +23534,11 @@
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>995</v>
       </c>
@@ -21673,8 +23551,11 @@
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="4" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>995</v>
       </c>
@@ -21687,8 +23568,11 @@
       <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>995</v>
       </c>
@@ -21701,8 +23585,11 @@
       <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>995</v>
       </c>
@@ -21715,8 +23602,11 @@
       <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>995</v>
       </c>
@@ -21729,8 +23619,11 @@
       <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>995</v>
       </c>
@@ -21743,8 +23636,11 @@
       <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>995</v>
       </c>
@@ -21756,6 +23652,9 @@
       </c>
       <c r="D10" s="3">
         <v>9</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>1176</v>
       </c>
     </row>
   </sheetData>
@@ -21765,15 +23664,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F90CCC3-E904-A247-9524-E51C14F69377}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>343</v>
       </c>
@@ -21786,8 +23686,11 @@
       <c r="D1" s="2" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21800,8 +23703,11 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21814,8 +23720,11 @@
       <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21828,8 +23737,11 @@
       <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="4" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21842,8 +23754,11 @@
       <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21856,8 +23771,11 @@
       <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="4" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21870,8 +23788,11 @@
       <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="4" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21884,8 +23805,11 @@
       <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21898,8 +23822,11 @@
       <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21912,8 +23839,11 @@
       <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21926,8 +23856,11 @@
       <c r="D11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21940,8 +23873,11 @@
       <c r="D12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21954,8 +23890,11 @@
       <c r="D13" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21968,8 +23907,11 @@
       <c r="D14" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21982,8 +23924,11 @@
       <c r="D15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>1004</v>
       </c>
@@ -21996,8 +23941,11 @@
       <c r="D16" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22010,8 +23958,11 @@
       <c r="D17" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="4" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22024,8 +23975,11 @@
       <c r="D18" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="4" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22038,8 +23992,11 @@
       <c r="D19" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="4" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22052,8 +24009,11 @@
       <c r="D20" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="4" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22066,8 +24026,11 @@
       <c r="D21" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="4" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22080,8 +24043,11 @@
       <c r="D22" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="4" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22094,8 +24060,11 @@
       <c r="D23" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="4" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22108,8 +24077,11 @@
       <c r="D24" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="4" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22122,8 +24094,11 @@
       <c r="D25" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="4" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22136,8 +24111,11 @@
       <c r="D26" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="4" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22150,8 +24128,11 @@
       <c r="D27" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="4" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22164,8 +24145,11 @@
       <c r="D28" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="4" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22178,8 +24162,11 @@
       <c r="D29" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E29" s="4" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22192,8 +24179,11 @@
       <c r="D30" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="4" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22206,8 +24196,11 @@
       <c r="D31" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="4" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>1004</v>
       </c>
@@ -22219,6 +24212,9 @@
       </c>
       <c r="D32" s="3">
         <v>31</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>1207</v>
       </c>
     </row>
   </sheetData>
@@ -22227,751 +24223,911 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="2" t="str">
-        <v>Country</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>SAP Value</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>EC Value</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>No.</v>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>01</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <v>VI</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v>02</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <v>AB</v>
-      </c>
-      <c r="D3" s="3" t="n">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B4" s="4" t="str">
-        <v>03</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <v>A</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="E3" s="4" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B5" s="4" t="str">
-        <v>04</v>
-      </c>
-      <c r="C5" s="4" t="str">
-        <v>AL</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="E4" s="4" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B6" s="4" t="str">
-        <v>05</v>
-      </c>
-      <c r="C6" s="4" t="str">
-        <v>AV</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="E5" s="4" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B7" s="4" t="str">
-        <v>06</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <v>BA</v>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="E6" s="4" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B8" s="4" t="str">
-        <v>07</v>
-      </c>
-      <c r="C8" s="4" t="str">
-        <v>PM</v>
-      </c>
-      <c r="D8" s="3" t="n">
+      <c r="E7" s="4" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B9" s="4" t="str">
-        <v>08</v>
-      </c>
-      <c r="C9" s="4" t="str">
-        <v>BA1</v>
-      </c>
-      <c r="D9" s="3" t="n">
+      <c r="E8" s="4" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B10" s="4" t="str">
-        <v>09</v>
-      </c>
-      <c r="C10" s="4" t="str">
-        <v>BU</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="E9" s="4" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B11" s="4" t="str">
+      <c r="E10" s="4" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="str">
-        <v>CC</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B12" s="4" t="str">
+      <c r="E11" s="4" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="str">
-        <v>CA</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B13" s="4" t="str">
+      <c r="E12" s="4" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="D13" s="3">
         <v>12</v>
       </c>
-      <c r="C13" s="4" t="str">
-        <v>CS</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B14" s="4" t="str">
+      <c r="E13" s="4" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="D14" s="3">
         <v>13</v>
       </c>
-      <c r="C14" s="4" t="str">
-        <v>CR</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B15" s="4" t="str">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="str">
-        <v>CO</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B16" s="4" t="str">
+      <c r="E14" s="4" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3">
+        <v>14</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D16" s="3">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="str">
-        <v>C</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B17" s="4" t="str">
+      <c r="E16" s="4" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="D17" s="3">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="str">
-        <v>CU</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B18" s="4" t="str">
+      <c r="E17" s="4" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D18" s="3">
         <v>17</v>
       </c>
-      <c r="C18" s="4" t="str">
-        <v>GI</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B19" s="4" t="str">
+      <c r="E18" s="4" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="3">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="str">
-        <v>GR</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B20" s="4" t="str">
+      <c r="E19" s="4" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="str">
-        <v>GU</v>
-      </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="4" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D23" s="3">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D24" s="3">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D25" s="3">
+        <v>24</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D26" s="3">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D29" s="3">
+        <v>28</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="D32" s="3">
+        <v>31</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="3">
+        <v>32</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D34" s="3">
+        <v>33</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D35" s="3">
+        <v>34</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D36" s="3">
+        <v>35</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D37" s="3">
+        <v>36</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D38" s="3">
+        <v>37</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="3">
+        <v>38</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D40" s="3">
+        <v>39</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="D41" s="3">
+        <v>40</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="D42" s="3">
+        <v>41</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="3">
+        <v>42</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D44" s="3">
+        <v>43</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D45" s="3">
+        <v>44</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D46" s="3">
+        <v>45</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D47" s="3">
+        <v>46</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="3">
+        <v>47</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D49" s="3">
+        <v>48</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D50" s="3">
+        <v>49</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D51" s="3">
+        <v>50</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B21" s="4" t="str">
-        <v>20</v>
-      </c>
-      <c r="C21" s="4" t="str">
-        <v>SS</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B22" s="4" t="str">
-        <v>21</v>
-      </c>
-      <c r="C22" s="4" t="str">
-        <v>H</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B23" s="4" t="str">
-        <v>22</v>
-      </c>
-      <c r="C23" s="4" t="str">
-        <v>HU</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B24" s="4" t="str">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4" t="str">
-        <v>J</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B25" s="4" t="str">
+      <c r="D52" s="3">
+        <v>51</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="4" t="str">
-        <v>LE</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B26" s="4" t="str">
-        <v>25</v>
-      </c>
-      <c r="C26" s="4" t="str">
-        <v>L</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B27" s="4" t="str">
-        <v>26</v>
-      </c>
-      <c r="C27" s="4" t="str">
-        <v>LO</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B28" s="4" t="str">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4" t="str">
-        <v>LU</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B29" s="4" t="str">
-        <v>28</v>
-      </c>
-      <c r="C29" s="4" t="str">
-        <v>M</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B30" s="4" t="str">
-        <v>29</v>
-      </c>
-      <c r="C30" s="4" t="str">
-        <v>MA</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B31" s="4" t="str">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="str">
-        <v>MU</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B32" s="4" t="str">
-        <v>31</v>
-      </c>
-      <c r="C32" s="4" t="str">
-        <v>NA</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B33" s="4" t="str">
-        <v>32</v>
-      </c>
-      <c r="C33" s="4" t="str">
-        <v>OR</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B34" s="4" t="str">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="str">
-        <v>O</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B35" s="4" t="str">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="str">
-        <v>P</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B36" s="4" t="str">
-        <v>35</v>
-      </c>
-      <c r="C36" s="4" t="str">
-        <v>GC</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B37" s="4" t="str">
-        <v>36</v>
-      </c>
-      <c r="C37" s="4" t="str">
-        <v>PO</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B38" s="4" t="str">
-        <v>37</v>
-      </c>
-      <c r="C38" s="4" t="str">
-        <v>SA</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B39" s="4" t="str">
-        <v>38</v>
-      </c>
-      <c r="C39" s="4" t="str">
-        <v>TF</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B40" s="4" t="str">
-        <v>39</v>
-      </c>
-      <c r="C40" s="4" t="str">
-        <v>S</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B41" s="4" t="str">
-        <v>40</v>
-      </c>
-      <c r="C41" s="4" t="str">
-        <v>SG</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B42" s="4" t="str">
-        <v>41</v>
-      </c>
-      <c r="C42" s="4" t="str">
-        <v>SE</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B43" s="4" t="str">
-        <v>42</v>
-      </c>
-      <c r="C43" s="4" t="str">
-        <v>SO</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B44" s="4" t="str">
-        <v>43</v>
-      </c>
-      <c r="C44" s="4" t="str">
-        <v>T</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B45" s="4" t="str">
-        <v>44</v>
-      </c>
-      <c r="C45" s="4" t="str">
-        <v>TE</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B46" s="4" t="str">
-        <v>45</v>
-      </c>
-      <c r="C46" s="4" t="str">
-        <v>TO</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B47" s="4" t="str">
-        <v>46</v>
-      </c>
-      <c r="C47" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B48" s="4" t="str">
-        <v>47</v>
-      </c>
-      <c r="C48" s="4" t="str">
-        <v>VA</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B49" s="4" t="str">
-        <v>48</v>
-      </c>
-      <c r="C49" s="4" t="str">
-        <v>BI</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B50" s="4" t="str">
-        <v>49</v>
-      </c>
-      <c r="C50" s="4" t="str">
-        <v>ZA</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B51" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="C51" s="4" t="str">
-        <v>Z</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="4" t="str">
-        <v>CE</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="3" t="str">
-        <v>Spain</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="4" t="str">
-        <v>ML</v>
-      </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="3">
         <v>52</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -22980,171 +25136,211 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="2" t="str">
-        <v>Country</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>SAP Value</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>EC Value</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>No.</v>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="3" t="str">
-        <v>Netherlands</v>
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="4" t="str">
-        <v>DR</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="C2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="4" t="str">
-        <v>FL</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E3" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="4" t="str">
-        <v>FR</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E4" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="4" t="str">
-        <v>GE</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E5" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="4" t="str">
-        <v>GR</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E6" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="4" t="str">
-        <v>LI</v>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="C7" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E7" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="4" t="str">
-        <v>NB</v>
-      </c>
-      <c r="D8" s="3" t="n">
+      <c r="C8" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E8" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="4" t="str">
-        <v>NH</v>
-      </c>
-      <c r="D9" s="3" t="n">
+      <c r="C9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E9" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="4" t="str">
-        <v>OV</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E10" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="4" t="str">
-        <v>ZH</v>
-      </c>
-      <c r="D11" s="3" t="n">
+      <c r="C11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E11" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="4" t="str">
-        <v>UT</v>
-      </c>
-      <c r="D12" s="3" t="n">
+      <c r="C12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="3" t="str">
-        <v>Netherlands</v>
+      <c r="E12" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>1284</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="4" t="str">
-        <v>ZE</v>
-      </c>
-      <c r="D13" s="3" t="n">
+      <c r="C13" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="3">
         <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
